--- a/프로젝트_트랙커.xlsx
+++ b/프로젝트_트랙커.xlsx
@@ -8,18 +8,20 @@
   </bookViews>
   <sheets>
     <sheet name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="설정" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="프로젝트" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="작업" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="프로젝트" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="작업" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="프로젝트 상세" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="간트차트" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="설정" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="상태목록">설정!$B$6:$B$10</definedName>
     <definedName name="우선순위목록">설정!$C$6:$C$8</definedName>
     <definedName name="분류목록">설정!$D$6:$D$11</definedName>
     <definedName name="팀원목록">설정!$E$6:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'프로젝트'!$B$5:$M$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'작업'!$B$5:$L$105</definedName>
+    <definedName name="프로젝트ID목록">프로젝트!$B$6:$B$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'프로젝트'!$B$5:$M$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'작업'!$B$5:$L$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +91,12 @@
       <b val="1"/>
       <color rgb="009C0006"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E75B6"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -273,10 +281,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -301,25 +309,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="15" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -332,19 +340,19 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -353,10 +361,10 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -365,10 +373,23 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -847,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M27"/>
+  <dimension ref="B1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1179,21 +1200,28 @@
     <row r="25">
       <c r="B25" s="36" t="inlineStr">
         <is>
-          <t>3. [간트차트] 시트에서 전체 일정을 한눈에 확인합니다. (파랑=진행, 초록=완료, 빨강=지연, 노랑 열=이번 주)</t>
+          <t>3. [프로젝트 상세] 시트에서 프로젝트를 선택하면 해당 프로젝트의 정보와 작업만 모아서 볼 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="36" t="inlineStr">
         <is>
-          <t>4. 이 대시보드는 자동으로 집계됩니다. 진행률은 프로젝트 시트에서 직접 입력하세요.</t>
+          <t>4. [간트차트] 시트에서 전체 일정을 한눈에 확인합니다. (파랑=진행, 초록=완료, 빨강=지연, 노랑 열=이번 주)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="36" t="inlineStr">
         <is>
-          <t>5. [설정] 시트에서 팀원·분류 등 드롭다운 목록을 수정할 수 있습니다.</t>
+          <t>5. 이 대시보드는 자동으로 집계됩니다. 진행률은 프로젝트 시트에서 직접 입력하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>6. [설정] 시트에서 팀원·분류 등 드롭다운 목록을 수정할 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -1226,200 +1254,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="37" t="inlineStr">
-        <is>
-          <t>⚙️ 설정 - 드롭다운 목록 관리</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="38" t="inlineStr">
-        <is>
-          <t>아래 목록을 수정하면 각 시트의 드롭다운 선택지가 바뀝니다. (항목 추가 시 이름 관리자에서 범위 확장 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>우선순위</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>분류</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>팀원</t>
-        </is>
-      </c>
-      <c r="G5" s="22" t="inlineStr">
-        <is>
-          <t>상태별 색상</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>디자인</t>
-        </is>
-      </c>
-      <c r="E7" s="24" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="G7" s="27" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>마케팅</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>박민수</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>정수진</t>
-        </is>
-      </c>
-      <c r="G9" s="31" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>지연</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>기획</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>최지훈</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr">
-        <is>
-          <t>지연</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3778,7 +3612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5702,6 +5536,3010 @@
     </dataValidation>
     <dataValidation sqref="E6:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=팀원목록</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:N70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>🔍 프로젝트 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>C5 셀에서 프로젝트를 선택하면 해당 프로젝트의 정보와 작업 목록이 자동으로 표시됩니다. 이 시트에는 데이터를 직접 입력하지 마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>프로젝트 선택</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>PRJ-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>프로젝트명</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>마감일</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>진행률</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>작업 수</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>완료 작업</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="43">
+        <f>IF($C$5="","",IFERROR(INDEX(프로젝트!$C$6:$C$105,MATCH($C$5,프로젝트!$B$6:$B$105,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="43">
+        <f>IF($C$5="","",IFERROR(INDEX(프로젝트!$D$6:$D$105,MATCH($C$5,프로젝트!$B$6:$B$105,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E8" s="43">
+        <f>IF($C$5="","",IFERROR(INDEX(프로젝트!$G$6:$G$105,MATCH($C$5,프로젝트!$B$6:$B$105,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F8" s="44">
+        <f>IF($C$5="","",IFERROR(INDEX(프로젝트!$H$6:$H$105,MATCH($C$5,프로젝트!$B$6:$B$105,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G8" s="44">
+        <f>IF($C$5="","",IFERROR(INDEX(프로젝트!$I$6:$I$105,MATCH($C$5,프로젝트!$B$6:$B$105,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H8" s="45">
+        <f>IF($C$5="","",IFERROR(INDEX(프로젝트!$J$6:$J$105,MATCH($C$5,프로젝트!$B$6:$B$105,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I8" s="43">
+        <f>IF($C$5="","",COUNTIFS(작업!$C$6:$C$105,$C$5,작업!$B$6:$B$105,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="J8" s="43">
+        <f>IF($C$5="","",COUNTIFS(작업!$C$6:$C$105,$C$5,작업!$G$6:$G$105,"완료"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>작업 ID</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>작업명</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>마감일</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>진행률</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>남은 일수</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="24">
+        <f>IF($N11="","",INDEX(작업!B$6:B$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="C11" s="39">
+        <f>IF($N11="","",INDEX(작업!D$6:D$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>IF($N11="","",INDEX(작업!E$6:E$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>IF($N11="","",INDEX(작업!F$6:F$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>IF($N11="","",INDEX(작업!G$6:G$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="40">
+        <f>IF($N11="","",INDEX(작업!H$6:H$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="H11" s="40">
+        <f>IF($N11="","",INDEX(작업!I$6:I$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="25">
+        <f>IF($N11="","",INDEX(작업!J$6:J$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="24">
+        <f>IF($N11="","",INDEX(작업!K$6:K$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="39">
+        <f>IF($N11="","",INDEX(작업!L$6:L$105,$N11))</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N11)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24">
+        <f>IF($N12="","",INDEX(작업!B$6:B$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="C12" s="39">
+        <f>IF($N12="","",INDEX(작업!D$6:D$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>IF($N12="","",INDEX(작업!E$6:E$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>IF($N12="","",INDEX(작업!F$6:F$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>IF($N12="","",INDEX(작업!G$6:G$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="40">
+        <f>IF($N12="","",INDEX(작업!H$6:H$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="H12" s="40">
+        <f>IF($N12="","",INDEX(작업!I$6:I$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="25">
+        <f>IF($N12="","",INDEX(작업!J$6:J$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="24">
+        <f>IF($N12="","",INDEX(작업!K$6:K$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="39">
+        <f>IF($N12="","",INDEX(작업!L$6:L$105,$N12))</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N12)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="24">
+        <f>IF($N13="","",INDEX(작업!B$6:B$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="C13" s="39">
+        <f>IF($N13="","",INDEX(작업!D$6:D$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>IF($N13="","",INDEX(작업!E$6:E$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>IF($N13="","",INDEX(작업!F$6:F$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="F13" s="24">
+        <f>IF($N13="","",INDEX(작업!G$6:G$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="40">
+        <f>IF($N13="","",INDEX(작업!H$6:H$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="H13" s="40">
+        <f>IF($N13="","",INDEX(작업!I$6:I$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="I13" s="25">
+        <f>IF($N13="","",INDEX(작업!J$6:J$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="24">
+        <f>IF($N13="","",INDEX(작업!K$6:K$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="39">
+        <f>IF($N13="","",INDEX(작업!L$6:L$105,$N13))</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N13)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="24">
+        <f>IF($N14="","",INDEX(작업!B$6:B$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="C14" s="39">
+        <f>IF($N14="","",INDEX(작업!D$6:D$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>IF($N14="","",INDEX(작업!E$6:E$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>IF($N14="","",INDEX(작업!F$6:F$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>IF($N14="","",INDEX(작업!G$6:G$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="40">
+        <f>IF($N14="","",INDEX(작업!H$6:H$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="H14" s="40">
+        <f>IF($N14="","",INDEX(작업!I$6:I$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="I14" s="25">
+        <f>IF($N14="","",INDEX(작업!J$6:J$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="24">
+        <f>IF($N14="","",INDEX(작업!K$6:K$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="39">
+        <f>IF($N14="","",INDEX(작업!L$6:L$105,$N14))</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N14)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="24">
+        <f>IF($N15="","",INDEX(작업!B$6:B$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="C15" s="39">
+        <f>IF($N15="","",INDEX(작업!D$6:D$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>IF($N15="","",INDEX(작업!E$6:E$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>IF($N15="","",INDEX(작업!F$6:F$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>IF($N15="","",INDEX(작업!G$6:G$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="40">
+        <f>IF($N15="","",INDEX(작업!H$6:H$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="40">
+        <f>IF($N15="","",INDEX(작업!I$6:I$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="I15" s="25">
+        <f>IF($N15="","",INDEX(작업!J$6:J$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="24">
+        <f>IF($N15="","",INDEX(작업!K$6:K$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="39">
+        <f>IF($N15="","",INDEX(작업!L$6:L$105,$N15))</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N15)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="24">
+        <f>IF($N16="","",INDEX(작업!B$6:B$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="39">
+        <f>IF($N16="","",INDEX(작업!D$6:D$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>IF($N16="","",INDEX(작업!E$6:E$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>IF($N16="","",INDEX(작업!F$6:F$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>IF($N16="","",INDEX(작업!G$6:G$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="40">
+        <f>IF($N16="","",INDEX(작업!H$6:H$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="40">
+        <f>IF($N16="","",INDEX(작업!I$6:I$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="I16" s="25">
+        <f>IF($N16="","",INDEX(작업!J$6:J$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="24">
+        <f>IF($N16="","",INDEX(작업!K$6:K$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="39">
+        <f>IF($N16="","",INDEX(작업!L$6:L$105,$N16))</f>
+        <v/>
+      </c>
+      <c r="N16">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N16)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="24">
+        <f>IF($N17="","",INDEX(작업!B$6:B$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="39">
+        <f>IF($N17="","",INDEX(작업!D$6:D$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>IF($N17="","",INDEX(작업!E$6:E$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>IF($N17="","",INDEX(작업!F$6:F$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="F17" s="24">
+        <f>IF($N17="","",INDEX(작업!G$6:G$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="40">
+        <f>IF($N17="","",INDEX(작업!H$6:H$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="40">
+        <f>IF($N17="","",INDEX(작업!I$6:I$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="I17" s="25">
+        <f>IF($N17="","",INDEX(작업!J$6:J$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="24">
+        <f>IF($N17="","",INDEX(작업!K$6:K$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="39">
+        <f>IF($N17="","",INDEX(작업!L$6:L$105,$N17))</f>
+        <v/>
+      </c>
+      <c r="N17">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N17)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="24">
+        <f>IF($N18="","",INDEX(작업!B$6:B$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="C18" s="39">
+        <f>IF($N18="","",INDEX(작업!D$6:D$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>IF($N18="","",INDEX(작업!E$6:E$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>IF($N18="","",INDEX(작업!F$6:F$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
+        <f>IF($N18="","",INDEX(작업!G$6:G$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="40">
+        <f>IF($N18="","",INDEX(작업!H$6:H$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="40">
+        <f>IF($N18="","",INDEX(작업!I$6:I$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="I18" s="25">
+        <f>IF($N18="","",INDEX(작업!J$6:J$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="24">
+        <f>IF($N18="","",INDEX(작업!K$6:K$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="39">
+        <f>IF($N18="","",INDEX(작업!L$6:L$105,$N18))</f>
+        <v/>
+      </c>
+      <c r="N18">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N18)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="24">
+        <f>IF($N19="","",INDEX(작업!B$6:B$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="C19" s="39">
+        <f>IF($N19="","",INDEX(작업!D$6:D$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>IF($N19="","",INDEX(작업!E$6:E$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>IF($N19="","",INDEX(작업!F$6:F$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
+        <f>IF($N19="","",INDEX(작업!G$6:G$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="40">
+        <f>IF($N19="","",INDEX(작업!H$6:H$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="40">
+        <f>IF($N19="","",INDEX(작업!I$6:I$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="I19" s="25">
+        <f>IF($N19="","",INDEX(작업!J$6:J$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="24">
+        <f>IF($N19="","",INDEX(작업!K$6:K$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="39">
+        <f>IF($N19="","",INDEX(작업!L$6:L$105,$N19))</f>
+        <v/>
+      </c>
+      <c r="N19">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N19)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="24">
+        <f>IF($N20="","",INDEX(작업!B$6:B$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="C20" s="39">
+        <f>IF($N20="","",INDEX(작업!D$6:D$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>IF($N20="","",INDEX(작업!E$6:E$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>IF($N20="","",INDEX(작업!F$6:F$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>IF($N20="","",INDEX(작업!G$6:G$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="40">
+        <f>IF($N20="","",INDEX(작업!H$6:H$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="40">
+        <f>IF($N20="","",INDEX(작업!I$6:I$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="I20" s="25">
+        <f>IF($N20="","",INDEX(작업!J$6:J$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="24">
+        <f>IF($N20="","",INDEX(작업!K$6:K$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="39">
+        <f>IF($N20="","",INDEX(작업!L$6:L$105,$N20))</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N20)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="24">
+        <f>IF($N21="","",INDEX(작업!B$6:B$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="C21" s="39">
+        <f>IF($N21="","",INDEX(작업!D$6:D$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>IF($N21="","",INDEX(작업!E$6:E$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>IF($N21="","",INDEX(작업!F$6:F$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>IF($N21="","",INDEX(작업!G$6:G$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="40">
+        <f>IF($N21="","",INDEX(작업!H$6:H$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="40">
+        <f>IF($N21="","",INDEX(작업!I$6:I$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="I21" s="25">
+        <f>IF($N21="","",INDEX(작업!J$6:J$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="24">
+        <f>IF($N21="","",INDEX(작업!K$6:K$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="39">
+        <f>IF($N21="","",INDEX(작업!L$6:L$105,$N21))</f>
+        <v/>
+      </c>
+      <c r="N21">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N21)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="24">
+        <f>IF($N22="","",INDEX(작업!B$6:B$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="C22" s="39">
+        <f>IF($N22="","",INDEX(작업!D$6:D$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="D22" s="24">
+        <f>IF($N22="","",INDEX(작업!E$6:E$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>IF($N22="","",INDEX(작업!F$6:F$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="F22" s="24">
+        <f>IF($N22="","",INDEX(작업!G$6:G$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="40">
+        <f>IF($N22="","",INDEX(작업!H$6:H$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="40">
+        <f>IF($N22="","",INDEX(작업!I$6:I$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="I22" s="25">
+        <f>IF($N22="","",INDEX(작업!J$6:J$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="24">
+        <f>IF($N22="","",INDEX(작업!K$6:K$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="39">
+        <f>IF($N22="","",INDEX(작업!L$6:L$105,$N22))</f>
+        <v/>
+      </c>
+      <c r="N22">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N22)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="24">
+        <f>IF($N23="","",INDEX(작업!B$6:B$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="C23" s="39">
+        <f>IF($N23="","",INDEX(작업!D$6:D$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>IF($N23="","",INDEX(작업!E$6:E$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>IF($N23="","",INDEX(작업!F$6:F$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="F23" s="24">
+        <f>IF($N23="","",INDEX(작업!G$6:G$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="40">
+        <f>IF($N23="","",INDEX(작업!H$6:H$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="40">
+        <f>IF($N23="","",INDEX(작업!I$6:I$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="I23" s="25">
+        <f>IF($N23="","",INDEX(작업!J$6:J$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="24">
+        <f>IF($N23="","",INDEX(작업!K$6:K$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="39">
+        <f>IF($N23="","",INDEX(작업!L$6:L$105,$N23))</f>
+        <v/>
+      </c>
+      <c r="N23">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N23)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="24">
+        <f>IF($N24="","",INDEX(작업!B$6:B$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="C24" s="39">
+        <f>IF($N24="","",INDEX(작업!D$6:D$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="D24" s="24">
+        <f>IF($N24="","",INDEX(작업!E$6:E$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>IF($N24="","",INDEX(작업!F$6:F$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="F24" s="24">
+        <f>IF($N24="","",INDEX(작업!G$6:G$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="40">
+        <f>IF($N24="","",INDEX(작업!H$6:H$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="H24" s="40">
+        <f>IF($N24="","",INDEX(작업!I$6:I$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="I24" s="25">
+        <f>IF($N24="","",INDEX(작업!J$6:J$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="24">
+        <f>IF($N24="","",INDEX(작업!K$6:K$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="39">
+        <f>IF($N24="","",INDEX(작업!L$6:L$105,$N24))</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N24)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="24">
+        <f>IF($N25="","",INDEX(작업!B$6:B$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="C25" s="39">
+        <f>IF($N25="","",INDEX(작업!D$6:D$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>IF($N25="","",INDEX(작업!E$6:E$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>IF($N25="","",INDEX(작업!F$6:F$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>IF($N25="","",INDEX(작업!G$6:G$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="40">
+        <f>IF($N25="","",INDEX(작업!H$6:H$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="H25" s="40">
+        <f>IF($N25="","",INDEX(작업!I$6:I$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="I25" s="25">
+        <f>IF($N25="","",INDEX(작업!J$6:J$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="24">
+        <f>IF($N25="","",INDEX(작업!K$6:K$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="39">
+        <f>IF($N25="","",INDEX(작업!L$6:L$105,$N25))</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N25)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="24">
+        <f>IF($N26="","",INDEX(작업!B$6:B$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="C26" s="39">
+        <f>IF($N26="","",INDEX(작업!D$6:D$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>IF($N26="","",INDEX(작업!E$6:E$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>IF($N26="","",INDEX(작업!F$6:F$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
+        <f>IF($N26="","",INDEX(작업!G$6:G$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="40">
+        <f>IF($N26="","",INDEX(작업!H$6:H$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="H26" s="40">
+        <f>IF($N26="","",INDEX(작업!I$6:I$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="I26" s="25">
+        <f>IF($N26="","",INDEX(작업!J$6:J$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="24">
+        <f>IF($N26="","",INDEX(작업!K$6:K$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="39">
+        <f>IF($N26="","",INDEX(작업!L$6:L$105,$N26))</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N26)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="24">
+        <f>IF($N27="","",INDEX(작업!B$6:B$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="C27" s="39">
+        <f>IF($N27="","",INDEX(작업!D$6:D$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>IF($N27="","",INDEX(작업!E$6:E$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>IF($N27="","",INDEX(작업!F$6:F$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="F27" s="24">
+        <f>IF($N27="","",INDEX(작업!G$6:G$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="40">
+        <f>IF($N27="","",INDEX(작업!H$6:H$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="H27" s="40">
+        <f>IF($N27="","",INDEX(작업!I$6:I$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="I27" s="25">
+        <f>IF($N27="","",INDEX(작업!J$6:J$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="24">
+        <f>IF($N27="","",INDEX(작업!K$6:K$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="39">
+        <f>IF($N27="","",INDEX(작업!L$6:L$105,$N27))</f>
+        <v/>
+      </c>
+      <c r="N27">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N27)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="24">
+        <f>IF($N28="","",INDEX(작업!B$6:B$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="C28" s="39">
+        <f>IF($N28="","",INDEX(작업!D$6:D$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="D28" s="24">
+        <f>IF($N28="","",INDEX(작업!E$6:E$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>IF($N28="","",INDEX(작업!F$6:F$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="F28" s="24">
+        <f>IF($N28="","",INDEX(작업!G$6:G$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="40">
+        <f>IF($N28="","",INDEX(작업!H$6:H$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="H28" s="40">
+        <f>IF($N28="","",INDEX(작업!I$6:I$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="I28" s="25">
+        <f>IF($N28="","",INDEX(작업!J$6:J$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="24">
+        <f>IF($N28="","",INDEX(작업!K$6:K$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="39">
+        <f>IF($N28="","",INDEX(작업!L$6:L$105,$N28))</f>
+        <v/>
+      </c>
+      <c r="N28">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N28)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="24">
+        <f>IF($N29="","",INDEX(작업!B$6:B$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="C29" s="39">
+        <f>IF($N29="","",INDEX(작업!D$6:D$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>IF($N29="","",INDEX(작업!E$6:E$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>IF($N29="","",INDEX(작업!F$6:F$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="F29" s="24">
+        <f>IF($N29="","",INDEX(작업!G$6:G$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="40">
+        <f>IF($N29="","",INDEX(작업!H$6:H$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="H29" s="40">
+        <f>IF($N29="","",INDEX(작업!I$6:I$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="I29" s="25">
+        <f>IF($N29="","",INDEX(작업!J$6:J$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="J29" s="24">
+        <f>IF($N29="","",INDEX(작업!K$6:K$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="39">
+        <f>IF($N29="","",INDEX(작업!L$6:L$105,$N29))</f>
+        <v/>
+      </c>
+      <c r="N29">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N29)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="24">
+        <f>IF($N30="","",INDEX(작업!B$6:B$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="C30" s="39">
+        <f>IF($N30="","",INDEX(작업!D$6:D$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="D30" s="24">
+        <f>IF($N30="","",INDEX(작업!E$6:E$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>IF($N30="","",INDEX(작업!F$6:F$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="F30" s="24">
+        <f>IF($N30="","",INDEX(작업!G$6:G$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="40">
+        <f>IF($N30="","",INDEX(작업!H$6:H$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="H30" s="40">
+        <f>IF($N30="","",INDEX(작업!I$6:I$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="I30" s="25">
+        <f>IF($N30="","",INDEX(작업!J$6:J$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="24">
+        <f>IF($N30="","",INDEX(작업!K$6:K$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="39">
+        <f>IF($N30="","",INDEX(작업!L$6:L$105,$N30))</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N30)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="24">
+        <f>IF($N31="","",INDEX(작업!B$6:B$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="C31" s="39">
+        <f>IF($N31="","",INDEX(작업!D$6:D$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="D31" s="24">
+        <f>IF($N31="","",INDEX(작업!E$6:E$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>IF($N31="","",INDEX(작업!F$6:F$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="F31" s="24">
+        <f>IF($N31="","",INDEX(작업!G$6:G$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="G31" s="40">
+        <f>IF($N31="","",INDEX(작업!H$6:H$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="H31" s="40">
+        <f>IF($N31="","",INDEX(작업!I$6:I$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="I31" s="25">
+        <f>IF($N31="","",INDEX(작업!J$6:J$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="24">
+        <f>IF($N31="","",INDEX(작업!K$6:K$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="39">
+        <f>IF($N31="","",INDEX(작업!L$6:L$105,$N31))</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N31)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="24">
+        <f>IF($N32="","",INDEX(작업!B$6:B$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="C32" s="39">
+        <f>IF($N32="","",INDEX(작업!D$6:D$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="D32" s="24">
+        <f>IF($N32="","",INDEX(작업!E$6:E$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="E32" s="24">
+        <f>IF($N32="","",INDEX(작업!F$6:F$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="F32" s="24">
+        <f>IF($N32="","",INDEX(작업!G$6:G$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="G32" s="40">
+        <f>IF($N32="","",INDEX(작업!H$6:H$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="H32" s="40">
+        <f>IF($N32="","",INDEX(작업!I$6:I$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="I32" s="25">
+        <f>IF($N32="","",INDEX(작업!J$6:J$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="J32" s="24">
+        <f>IF($N32="","",INDEX(작업!K$6:K$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="39">
+        <f>IF($N32="","",INDEX(작업!L$6:L$105,$N32))</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N32)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="24">
+        <f>IF($N33="","",INDEX(작업!B$6:B$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="C33" s="39">
+        <f>IF($N33="","",INDEX(작업!D$6:D$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="D33" s="24">
+        <f>IF($N33="","",INDEX(작업!E$6:E$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="E33" s="24">
+        <f>IF($N33="","",INDEX(작업!F$6:F$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="F33" s="24">
+        <f>IF($N33="","",INDEX(작업!G$6:G$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="G33" s="40">
+        <f>IF($N33="","",INDEX(작업!H$6:H$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="H33" s="40">
+        <f>IF($N33="","",INDEX(작업!I$6:I$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="I33" s="25">
+        <f>IF($N33="","",INDEX(작업!J$6:J$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="24">
+        <f>IF($N33="","",INDEX(작업!K$6:K$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="39">
+        <f>IF($N33="","",INDEX(작업!L$6:L$105,$N33))</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N33)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="24">
+        <f>IF($N34="","",INDEX(작업!B$6:B$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="C34" s="39">
+        <f>IF($N34="","",INDEX(작업!D$6:D$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="D34" s="24">
+        <f>IF($N34="","",INDEX(작업!E$6:E$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="E34" s="24">
+        <f>IF($N34="","",INDEX(작업!F$6:F$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="F34" s="24">
+        <f>IF($N34="","",INDEX(작업!G$6:G$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="G34" s="40">
+        <f>IF($N34="","",INDEX(작업!H$6:H$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="H34" s="40">
+        <f>IF($N34="","",INDEX(작업!I$6:I$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="I34" s="25">
+        <f>IF($N34="","",INDEX(작업!J$6:J$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="24">
+        <f>IF($N34="","",INDEX(작업!K$6:K$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="39">
+        <f>IF($N34="","",INDEX(작업!L$6:L$105,$N34))</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N34)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="24">
+        <f>IF($N35="","",INDEX(작업!B$6:B$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="C35" s="39">
+        <f>IF($N35="","",INDEX(작업!D$6:D$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="D35" s="24">
+        <f>IF($N35="","",INDEX(작업!E$6:E$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>IF($N35="","",INDEX(작업!F$6:F$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>IF($N35="","",INDEX(작업!G$6:G$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="G35" s="40">
+        <f>IF($N35="","",INDEX(작업!H$6:H$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="H35" s="40">
+        <f>IF($N35="","",INDEX(작업!I$6:I$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="I35" s="25">
+        <f>IF($N35="","",INDEX(작업!J$6:J$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="24">
+        <f>IF($N35="","",INDEX(작업!K$6:K$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="39">
+        <f>IF($N35="","",INDEX(작업!L$6:L$105,$N35))</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N35)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="24">
+        <f>IF($N36="","",INDEX(작업!B$6:B$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="C36" s="39">
+        <f>IF($N36="","",INDEX(작업!D$6:D$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="D36" s="24">
+        <f>IF($N36="","",INDEX(작업!E$6:E$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>IF($N36="","",INDEX(작업!F$6:F$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>IF($N36="","",INDEX(작업!G$6:G$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="G36" s="40">
+        <f>IF($N36="","",INDEX(작업!H$6:H$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="H36" s="40">
+        <f>IF($N36="","",INDEX(작업!I$6:I$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="I36" s="25">
+        <f>IF($N36="","",INDEX(작업!J$6:J$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="24">
+        <f>IF($N36="","",INDEX(작업!K$6:K$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="39">
+        <f>IF($N36="","",INDEX(작업!L$6:L$105,$N36))</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N36)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="24">
+        <f>IF($N37="","",INDEX(작업!B$6:B$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="C37" s="39">
+        <f>IF($N37="","",INDEX(작업!D$6:D$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="D37" s="24">
+        <f>IF($N37="","",INDEX(작업!E$6:E$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>IF($N37="","",INDEX(작업!F$6:F$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>IF($N37="","",INDEX(작업!G$6:G$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="40">
+        <f>IF($N37="","",INDEX(작업!H$6:H$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="H37" s="40">
+        <f>IF($N37="","",INDEX(작업!I$6:I$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="I37" s="25">
+        <f>IF($N37="","",INDEX(작업!J$6:J$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="24">
+        <f>IF($N37="","",INDEX(작업!K$6:K$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="39">
+        <f>IF($N37="","",INDEX(작업!L$6:L$105,$N37))</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N37)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="24">
+        <f>IF($N38="","",INDEX(작업!B$6:B$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="C38" s="39">
+        <f>IF($N38="","",INDEX(작업!D$6:D$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="D38" s="24">
+        <f>IF($N38="","",INDEX(작업!E$6:E$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="E38" s="24">
+        <f>IF($N38="","",INDEX(작업!F$6:F$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="F38" s="24">
+        <f>IF($N38="","",INDEX(작업!G$6:G$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="G38" s="40">
+        <f>IF($N38="","",INDEX(작업!H$6:H$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="H38" s="40">
+        <f>IF($N38="","",INDEX(작업!I$6:I$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="I38" s="25">
+        <f>IF($N38="","",INDEX(작업!J$6:J$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="24">
+        <f>IF($N38="","",INDEX(작업!K$6:K$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="39">
+        <f>IF($N38="","",INDEX(작업!L$6:L$105,$N38))</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N38)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="24">
+        <f>IF($N39="","",INDEX(작업!B$6:B$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="C39" s="39">
+        <f>IF($N39="","",INDEX(작업!D$6:D$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="D39" s="24">
+        <f>IF($N39="","",INDEX(작업!E$6:E$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="24">
+        <f>IF($N39="","",INDEX(작업!F$6:F$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="F39" s="24">
+        <f>IF($N39="","",INDEX(작업!G$6:G$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="40">
+        <f>IF($N39="","",INDEX(작업!H$6:H$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="H39" s="40">
+        <f>IF($N39="","",INDEX(작업!I$6:I$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="I39" s="25">
+        <f>IF($N39="","",INDEX(작업!J$6:J$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="24">
+        <f>IF($N39="","",INDEX(작업!K$6:K$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="39">
+        <f>IF($N39="","",INDEX(작업!L$6:L$105,$N39))</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N39)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="24">
+        <f>IF($N40="","",INDEX(작업!B$6:B$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="C40" s="39">
+        <f>IF($N40="","",INDEX(작업!D$6:D$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="D40" s="24">
+        <f>IF($N40="","",INDEX(작업!E$6:E$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="E40" s="24">
+        <f>IF($N40="","",INDEX(작업!F$6:F$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="F40" s="24">
+        <f>IF($N40="","",INDEX(작업!G$6:G$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="G40" s="40">
+        <f>IF($N40="","",INDEX(작업!H$6:H$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="H40" s="40">
+        <f>IF($N40="","",INDEX(작업!I$6:I$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="I40" s="25">
+        <f>IF($N40="","",INDEX(작업!J$6:J$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="24">
+        <f>IF($N40="","",INDEX(작업!K$6:K$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="39">
+        <f>IF($N40="","",INDEX(작업!L$6:L$105,$N40))</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N40)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="24">
+        <f>IF($N41="","",INDEX(작업!B$6:B$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="C41" s="39">
+        <f>IF($N41="","",INDEX(작업!D$6:D$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="D41" s="24">
+        <f>IF($N41="","",INDEX(작업!E$6:E$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="E41" s="24">
+        <f>IF($N41="","",INDEX(작업!F$6:F$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="F41" s="24">
+        <f>IF($N41="","",INDEX(작업!G$6:G$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="G41" s="40">
+        <f>IF($N41="","",INDEX(작업!H$6:H$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="H41" s="40">
+        <f>IF($N41="","",INDEX(작업!I$6:I$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="I41" s="25">
+        <f>IF($N41="","",INDEX(작업!J$6:J$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="J41" s="24">
+        <f>IF($N41="","",INDEX(작업!K$6:K$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="K41" s="39">
+        <f>IF($N41="","",INDEX(작업!L$6:L$105,$N41))</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N41)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="24">
+        <f>IF($N42="","",INDEX(작업!B$6:B$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="39">
+        <f>IF($N42="","",INDEX(작업!D$6:D$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="D42" s="24">
+        <f>IF($N42="","",INDEX(작업!E$6:E$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="24">
+        <f>IF($N42="","",INDEX(작업!F$6:F$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="24">
+        <f>IF($N42="","",INDEX(작업!G$6:G$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="40">
+        <f>IF($N42="","",INDEX(작업!H$6:H$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="40">
+        <f>IF($N42="","",INDEX(작업!I$6:I$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="I42" s="25">
+        <f>IF($N42="","",INDEX(작업!J$6:J$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="24">
+        <f>IF($N42="","",INDEX(작업!K$6:K$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="K42" s="39">
+        <f>IF($N42="","",INDEX(작업!L$6:L$105,$N42))</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N42)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="24">
+        <f>IF($N43="","",INDEX(작업!B$6:B$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="39">
+        <f>IF($N43="","",INDEX(작업!D$6:D$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="D43" s="24">
+        <f>IF($N43="","",INDEX(작업!E$6:E$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>IF($N43="","",INDEX(작업!F$6:F$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="F43" s="24">
+        <f>IF($N43="","",INDEX(작업!G$6:G$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="G43" s="40">
+        <f>IF($N43="","",INDEX(작업!H$6:H$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="H43" s="40">
+        <f>IF($N43="","",INDEX(작업!I$6:I$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="I43" s="25">
+        <f>IF($N43="","",INDEX(작업!J$6:J$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="J43" s="24">
+        <f>IF($N43="","",INDEX(작업!K$6:K$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="K43" s="39">
+        <f>IF($N43="","",INDEX(작업!L$6:L$105,$N43))</f>
+        <v/>
+      </c>
+      <c r="N43">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N43)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="24">
+        <f>IF($N44="","",INDEX(작업!B$6:B$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="39">
+        <f>IF($N44="","",INDEX(작업!D$6:D$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="D44" s="24">
+        <f>IF($N44="","",INDEX(작업!E$6:E$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="24">
+        <f>IF($N44="","",INDEX(작업!F$6:F$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="F44" s="24">
+        <f>IF($N44="","",INDEX(작업!G$6:G$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="G44" s="40">
+        <f>IF($N44="","",INDEX(작업!H$6:H$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="H44" s="40">
+        <f>IF($N44="","",INDEX(작업!I$6:I$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="I44" s="25">
+        <f>IF($N44="","",INDEX(작업!J$6:J$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="J44" s="24">
+        <f>IF($N44="","",INDEX(작업!K$6:K$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="K44" s="39">
+        <f>IF($N44="","",INDEX(작업!L$6:L$105,$N44))</f>
+        <v/>
+      </c>
+      <c r="N44">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N44)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="24">
+        <f>IF($N45="","",INDEX(작업!B$6:B$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="C45" s="39">
+        <f>IF($N45="","",INDEX(작업!D$6:D$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="D45" s="24">
+        <f>IF($N45="","",INDEX(작업!E$6:E$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="E45" s="24">
+        <f>IF($N45="","",INDEX(작업!F$6:F$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="F45" s="24">
+        <f>IF($N45="","",INDEX(작업!G$6:G$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="G45" s="40">
+        <f>IF($N45="","",INDEX(작업!H$6:H$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="H45" s="40">
+        <f>IF($N45="","",INDEX(작업!I$6:I$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="I45" s="25">
+        <f>IF($N45="","",INDEX(작업!J$6:J$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="J45" s="24">
+        <f>IF($N45="","",INDEX(작업!K$6:K$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="K45" s="39">
+        <f>IF($N45="","",INDEX(작업!L$6:L$105,$N45))</f>
+        <v/>
+      </c>
+      <c r="N45">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N45)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="24">
+        <f>IF($N46="","",INDEX(작업!B$6:B$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="C46" s="39">
+        <f>IF($N46="","",INDEX(작업!D$6:D$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="D46" s="24">
+        <f>IF($N46="","",INDEX(작업!E$6:E$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="E46" s="24">
+        <f>IF($N46="","",INDEX(작업!F$6:F$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="F46" s="24">
+        <f>IF($N46="","",INDEX(작업!G$6:G$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="G46" s="40">
+        <f>IF($N46="","",INDEX(작업!H$6:H$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="H46" s="40">
+        <f>IF($N46="","",INDEX(작업!I$6:I$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="I46" s="25">
+        <f>IF($N46="","",INDEX(작업!J$6:J$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="J46" s="24">
+        <f>IF($N46="","",INDEX(작업!K$6:K$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="K46" s="39">
+        <f>IF($N46="","",INDEX(작업!L$6:L$105,$N46))</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N46)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="24">
+        <f>IF($N47="","",INDEX(작업!B$6:B$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="C47" s="39">
+        <f>IF($N47="","",INDEX(작업!D$6:D$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="D47" s="24">
+        <f>IF($N47="","",INDEX(작업!E$6:E$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="E47" s="24">
+        <f>IF($N47="","",INDEX(작업!F$6:F$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="F47" s="24">
+        <f>IF($N47="","",INDEX(작업!G$6:G$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="G47" s="40">
+        <f>IF($N47="","",INDEX(작업!H$6:H$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="H47" s="40">
+        <f>IF($N47="","",INDEX(작업!I$6:I$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="I47" s="25">
+        <f>IF($N47="","",INDEX(작업!J$6:J$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="J47" s="24">
+        <f>IF($N47="","",INDEX(작업!K$6:K$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="K47" s="39">
+        <f>IF($N47="","",INDEX(작업!L$6:L$105,$N47))</f>
+        <v/>
+      </c>
+      <c r="N47">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N47)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="24">
+        <f>IF($N48="","",INDEX(작업!B$6:B$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="C48" s="39">
+        <f>IF($N48="","",INDEX(작업!D$6:D$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="D48" s="24">
+        <f>IF($N48="","",INDEX(작업!E$6:E$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="E48" s="24">
+        <f>IF($N48="","",INDEX(작업!F$6:F$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="F48" s="24">
+        <f>IF($N48="","",INDEX(작업!G$6:G$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="G48" s="40">
+        <f>IF($N48="","",INDEX(작업!H$6:H$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="H48" s="40">
+        <f>IF($N48="","",INDEX(작업!I$6:I$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="I48" s="25">
+        <f>IF($N48="","",INDEX(작업!J$6:J$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="J48" s="24">
+        <f>IF($N48="","",INDEX(작업!K$6:K$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="K48" s="39">
+        <f>IF($N48="","",INDEX(작업!L$6:L$105,$N48))</f>
+        <v/>
+      </c>
+      <c r="N48">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N48)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="24">
+        <f>IF($N49="","",INDEX(작업!B$6:B$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="C49" s="39">
+        <f>IF($N49="","",INDEX(작업!D$6:D$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="D49" s="24">
+        <f>IF($N49="","",INDEX(작업!E$6:E$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="E49" s="24">
+        <f>IF($N49="","",INDEX(작업!F$6:F$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="F49" s="24">
+        <f>IF($N49="","",INDEX(작업!G$6:G$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="G49" s="40">
+        <f>IF($N49="","",INDEX(작업!H$6:H$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="H49" s="40">
+        <f>IF($N49="","",INDEX(작업!I$6:I$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="I49" s="25">
+        <f>IF($N49="","",INDEX(작업!J$6:J$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="J49" s="24">
+        <f>IF($N49="","",INDEX(작업!K$6:K$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="K49" s="39">
+        <f>IF($N49="","",INDEX(작업!L$6:L$105,$N49))</f>
+        <v/>
+      </c>
+      <c r="N49">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N49)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="24">
+        <f>IF($N50="","",INDEX(작업!B$6:B$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="C50" s="39">
+        <f>IF($N50="","",INDEX(작업!D$6:D$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="D50" s="24">
+        <f>IF($N50="","",INDEX(작업!E$6:E$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="E50" s="24">
+        <f>IF($N50="","",INDEX(작업!F$6:F$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="F50" s="24">
+        <f>IF($N50="","",INDEX(작업!G$6:G$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="G50" s="40">
+        <f>IF($N50="","",INDEX(작업!H$6:H$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="H50" s="40">
+        <f>IF($N50="","",INDEX(작업!I$6:I$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="I50" s="25">
+        <f>IF($N50="","",INDEX(작업!J$6:J$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="J50" s="24">
+        <f>IF($N50="","",INDEX(작업!K$6:K$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="K50" s="39">
+        <f>IF($N50="","",INDEX(작업!L$6:L$105,$N50))</f>
+        <v/>
+      </c>
+      <c r="N50">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N50)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="24">
+        <f>IF($N51="","",INDEX(작업!B$6:B$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="C51" s="39">
+        <f>IF($N51="","",INDEX(작업!D$6:D$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="D51" s="24">
+        <f>IF($N51="","",INDEX(작업!E$6:E$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="E51" s="24">
+        <f>IF($N51="","",INDEX(작업!F$6:F$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="F51" s="24">
+        <f>IF($N51="","",INDEX(작업!G$6:G$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="G51" s="40">
+        <f>IF($N51="","",INDEX(작업!H$6:H$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="H51" s="40">
+        <f>IF($N51="","",INDEX(작업!I$6:I$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="I51" s="25">
+        <f>IF($N51="","",INDEX(작업!J$6:J$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="J51" s="24">
+        <f>IF($N51="","",INDEX(작업!K$6:K$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="K51" s="39">
+        <f>IF($N51="","",INDEX(작업!L$6:L$105,$N51))</f>
+        <v/>
+      </c>
+      <c r="N51">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N51)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="24">
+        <f>IF($N52="","",INDEX(작업!B$6:B$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="C52" s="39">
+        <f>IF($N52="","",INDEX(작업!D$6:D$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="D52" s="24">
+        <f>IF($N52="","",INDEX(작업!E$6:E$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="E52" s="24">
+        <f>IF($N52="","",INDEX(작업!F$6:F$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="F52" s="24">
+        <f>IF($N52="","",INDEX(작업!G$6:G$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="G52" s="40">
+        <f>IF($N52="","",INDEX(작업!H$6:H$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="H52" s="40">
+        <f>IF($N52="","",INDEX(작업!I$6:I$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="I52" s="25">
+        <f>IF($N52="","",INDEX(작업!J$6:J$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="J52" s="24">
+        <f>IF($N52="","",INDEX(작업!K$6:K$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="K52" s="39">
+        <f>IF($N52="","",INDEX(작업!L$6:L$105,$N52))</f>
+        <v/>
+      </c>
+      <c r="N52">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N52)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="24">
+        <f>IF($N53="","",INDEX(작업!B$6:B$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="C53" s="39">
+        <f>IF($N53="","",INDEX(작업!D$6:D$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="D53" s="24">
+        <f>IF($N53="","",INDEX(작업!E$6:E$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="E53" s="24">
+        <f>IF($N53="","",INDEX(작업!F$6:F$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="F53" s="24">
+        <f>IF($N53="","",INDEX(작업!G$6:G$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="G53" s="40">
+        <f>IF($N53="","",INDEX(작업!H$6:H$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="H53" s="40">
+        <f>IF($N53="","",INDEX(작업!I$6:I$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="I53" s="25">
+        <f>IF($N53="","",INDEX(작업!J$6:J$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="J53" s="24">
+        <f>IF($N53="","",INDEX(작업!K$6:K$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="K53" s="39">
+        <f>IF($N53="","",INDEX(작업!L$6:L$105,$N53))</f>
+        <v/>
+      </c>
+      <c r="N53">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N53)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="24">
+        <f>IF($N54="","",INDEX(작업!B$6:B$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="C54" s="39">
+        <f>IF($N54="","",INDEX(작업!D$6:D$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="D54" s="24">
+        <f>IF($N54="","",INDEX(작업!E$6:E$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="E54" s="24">
+        <f>IF($N54="","",INDEX(작업!F$6:F$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="F54" s="24">
+        <f>IF($N54="","",INDEX(작업!G$6:G$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="G54" s="40">
+        <f>IF($N54="","",INDEX(작업!H$6:H$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="H54" s="40">
+        <f>IF($N54="","",INDEX(작업!I$6:I$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="I54" s="25">
+        <f>IF($N54="","",INDEX(작업!J$6:J$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="J54" s="24">
+        <f>IF($N54="","",INDEX(작업!K$6:K$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="K54" s="39">
+        <f>IF($N54="","",INDEX(작업!L$6:L$105,$N54))</f>
+        <v/>
+      </c>
+      <c r="N54">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N54)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="24">
+        <f>IF($N55="","",INDEX(작업!B$6:B$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="C55" s="39">
+        <f>IF($N55="","",INDEX(작업!D$6:D$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="D55" s="24">
+        <f>IF($N55="","",INDEX(작업!E$6:E$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="E55" s="24">
+        <f>IF($N55="","",INDEX(작업!F$6:F$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="F55" s="24">
+        <f>IF($N55="","",INDEX(작업!G$6:G$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="G55" s="40">
+        <f>IF($N55="","",INDEX(작업!H$6:H$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="H55" s="40">
+        <f>IF($N55="","",INDEX(작업!I$6:I$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="I55" s="25">
+        <f>IF($N55="","",INDEX(작업!J$6:J$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="J55" s="24">
+        <f>IF($N55="","",INDEX(작업!K$6:K$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="K55" s="39">
+        <f>IF($N55="","",INDEX(작업!L$6:L$105,$N55))</f>
+        <v/>
+      </c>
+      <c r="N55">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N55)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="24">
+        <f>IF($N56="","",INDEX(작업!B$6:B$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="C56" s="39">
+        <f>IF($N56="","",INDEX(작업!D$6:D$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="D56" s="24">
+        <f>IF($N56="","",INDEX(작업!E$6:E$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="E56" s="24">
+        <f>IF($N56="","",INDEX(작업!F$6:F$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="F56" s="24">
+        <f>IF($N56="","",INDEX(작업!G$6:G$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="G56" s="40">
+        <f>IF($N56="","",INDEX(작업!H$6:H$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="H56" s="40">
+        <f>IF($N56="","",INDEX(작업!I$6:I$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="I56" s="25">
+        <f>IF($N56="","",INDEX(작업!J$6:J$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="J56" s="24">
+        <f>IF($N56="","",INDEX(작업!K$6:K$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="K56" s="39">
+        <f>IF($N56="","",INDEX(작업!L$6:L$105,$N56))</f>
+        <v/>
+      </c>
+      <c r="N56">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N56)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="24">
+        <f>IF($N57="","",INDEX(작업!B$6:B$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="C57" s="39">
+        <f>IF($N57="","",INDEX(작업!D$6:D$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="D57" s="24">
+        <f>IF($N57="","",INDEX(작업!E$6:E$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="E57" s="24">
+        <f>IF($N57="","",INDEX(작업!F$6:F$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="F57" s="24">
+        <f>IF($N57="","",INDEX(작업!G$6:G$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="G57" s="40">
+        <f>IF($N57="","",INDEX(작업!H$6:H$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="H57" s="40">
+        <f>IF($N57="","",INDEX(작업!I$6:I$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="I57" s="25">
+        <f>IF($N57="","",INDEX(작업!J$6:J$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="J57" s="24">
+        <f>IF($N57="","",INDEX(작업!K$6:K$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="K57" s="39">
+        <f>IF($N57="","",INDEX(작업!L$6:L$105,$N57))</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N57)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="24">
+        <f>IF($N58="","",INDEX(작업!B$6:B$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="C58" s="39">
+        <f>IF($N58="","",INDEX(작업!D$6:D$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="D58" s="24">
+        <f>IF($N58="","",INDEX(작업!E$6:E$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="E58" s="24">
+        <f>IF($N58="","",INDEX(작업!F$6:F$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="F58" s="24">
+        <f>IF($N58="","",INDEX(작업!G$6:G$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="G58" s="40">
+        <f>IF($N58="","",INDEX(작업!H$6:H$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="H58" s="40">
+        <f>IF($N58="","",INDEX(작업!I$6:I$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="I58" s="25">
+        <f>IF($N58="","",INDEX(작업!J$6:J$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="J58" s="24">
+        <f>IF($N58="","",INDEX(작업!K$6:K$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="K58" s="39">
+        <f>IF($N58="","",INDEX(작업!L$6:L$105,$N58))</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N58)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="24">
+        <f>IF($N59="","",INDEX(작업!B$6:B$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="C59" s="39">
+        <f>IF($N59="","",INDEX(작업!D$6:D$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="D59" s="24">
+        <f>IF($N59="","",INDEX(작업!E$6:E$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="E59" s="24">
+        <f>IF($N59="","",INDEX(작업!F$6:F$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="F59" s="24">
+        <f>IF($N59="","",INDEX(작업!G$6:G$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="G59" s="40">
+        <f>IF($N59="","",INDEX(작업!H$6:H$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="H59" s="40">
+        <f>IF($N59="","",INDEX(작업!I$6:I$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="I59" s="25">
+        <f>IF($N59="","",INDEX(작업!J$6:J$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="J59" s="24">
+        <f>IF($N59="","",INDEX(작업!K$6:K$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="K59" s="39">
+        <f>IF($N59="","",INDEX(작업!L$6:L$105,$N59))</f>
+        <v/>
+      </c>
+      <c r="N59">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N59)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="24">
+        <f>IF($N60="","",INDEX(작업!B$6:B$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="C60" s="39">
+        <f>IF($N60="","",INDEX(작업!D$6:D$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="D60" s="24">
+        <f>IF($N60="","",INDEX(작업!E$6:E$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="E60" s="24">
+        <f>IF($N60="","",INDEX(작업!F$6:F$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="F60" s="24">
+        <f>IF($N60="","",INDEX(작업!G$6:G$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="G60" s="40">
+        <f>IF($N60="","",INDEX(작업!H$6:H$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="H60" s="40">
+        <f>IF($N60="","",INDEX(작업!I$6:I$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="I60" s="25">
+        <f>IF($N60="","",INDEX(작업!J$6:J$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="J60" s="24">
+        <f>IF($N60="","",INDEX(작업!K$6:K$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="K60" s="39">
+        <f>IF($N60="","",INDEX(작업!L$6:L$105,$N60))</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N60)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="24">
+        <f>IF($N61="","",INDEX(작업!B$6:B$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="C61" s="39">
+        <f>IF($N61="","",INDEX(작업!D$6:D$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="D61" s="24">
+        <f>IF($N61="","",INDEX(작업!E$6:E$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="E61" s="24">
+        <f>IF($N61="","",INDEX(작업!F$6:F$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="F61" s="24">
+        <f>IF($N61="","",INDEX(작업!G$6:G$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="G61" s="40">
+        <f>IF($N61="","",INDEX(작업!H$6:H$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="H61" s="40">
+        <f>IF($N61="","",INDEX(작업!I$6:I$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="I61" s="25">
+        <f>IF($N61="","",INDEX(작업!J$6:J$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="J61" s="24">
+        <f>IF($N61="","",INDEX(작업!K$6:K$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="K61" s="39">
+        <f>IF($N61="","",INDEX(작업!L$6:L$105,$N61))</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N61)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="24">
+        <f>IF($N62="","",INDEX(작업!B$6:B$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="C62" s="39">
+        <f>IF($N62="","",INDEX(작업!D$6:D$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="D62" s="24">
+        <f>IF($N62="","",INDEX(작업!E$6:E$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="E62" s="24">
+        <f>IF($N62="","",INDEX(작업!F$6:F$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="F62" s="24">
+        <f>IF($N62="","",INDEX(작업!G$6:G$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="G62" s="40">
+        <f>IF($N62="","",INDEX(작업!H$6:H$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="H62" s="40">
+        <f>IF($N62="","",INDEX(작업!I$6:I$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="I62" s="25">
+        <f>IF($N62="","",INDEX(작업!J$6:J$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="J62" s="24">
+        <f>IF($N62="","",INDEX(작업!K$6:K$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="K62" s="39">
+        <f>IF($N62="","",INDEX(작업!L$6:L$105,$N62))</f>
+        <v/>
+      </c>
+      <c r="N62">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N62)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="24">
+        <f>IF($N63="","",INDEX(작업!B$6:B$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="C63" s="39">
+        <f>IF($N63="","",INDEX(작업!D$6:D$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="D63" s="24">
+        <f>IF($N63="","",INDEX(작업!E$6:E$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="E63" s="24">
+        <f>IF($N63="","",INDEX(작업!F$6:F$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="F63" s="24">
+        <f>IF($N63="","",INDEX(작업!G$6:G$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="G63" s="40">
+        <f>IF($N63="","",INDEX(작업!H$6:H$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="H63" s="40">
+        <f>IF($N63="","",INDEX(작업!I$6:I$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="I63" s="25">
+        <f>IF($N63="","",INDEX(작업!J$6:J$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="J63" s="24">
+        <f>IF($N63="","",INDEX(작업!K$6:K$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="K63" s="39">
+        <f>IF($N63="","",INDEX(작업!L$6:L$105,$N63))</f>
+        <v/>
+      </c>
+      <c r="N63">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N63)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="24">
+        <f>IF($N64="","",INDEX(작업!B$6:B$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="C64" s="39">
+        <f>IF($N64="","",INDEX(작업!D$6:D$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="D64" s="24">
+        <f>IF($N64="","",INDEX(작업!E$6:E$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="E64" s="24">
+        <f>IF($N64="","",INDEX(작업!F$6:F$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="F64" s="24">
+        <f>IF($N64="","",INDEX(작업!G$6:G$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="G64" s="40">
+        <f>IF($N64="","",INDEX(작업!H$6:H$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="H64" s="40">
+        <f>IF($N64="","",INDEX(작업!I$6:I$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="I64" s="25">
+        <f>IF($N64="","",INDEX(작업!J$6:J$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="J64" s="24">
+        <f>IF($N64="","",INDEX(작업!K$6:K$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="K64" s="39">
+        <f>IF($N64="","",INDEX(작업!L$6:L$105,$N64))</f>
+        <v/>
+      </c>
+      <c r="N64">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N64)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="24">
+        <f>IF($N65="","",INDEX(작업!B$6:B$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="C65" s="39">
+        <f>IF($N65="","",INDEX(작업!D$6:D$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="D65" s="24">
+        <f>IF($N65="","",INDEX(작업!E$6:E$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="E65" s="24">
+        <f>IF($N65="","",INDEX(작업!F$6:F$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="F65" s="24">
+        <f>IF($N65="","",INDEX(작업!G$6:G$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="G65" s="40">
+        <f>IF($N65="","",INDEX(작업!H$6:H$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="H65" s="40">
+        <f>IF($N65="","",INDEX(작업!I$6:I$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="I65" s="25">
+        <f>IF($N65="","",INDEX(작업!J$6:J$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="J65" s="24">
+        <f>IF($N65="","",INDEX(작업!K$6:K$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="K65" s="39">
+        <f>IF($N65="","",INDEX(작업!L$6:L$105,$N65))</f>
+        <v/>
+      </c>
+      <c r="N65">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N65)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="24">
+        <f>IF($N66="","",INDEX(작업!B$6:B$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="C66" s="39">
+        <f>IF($N66="","",INDEX(작업!D$6:D$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="D66" s="24">
+        <f>IF($N66="","",INDEX(작업!E$6:E$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="E66" s="24">
+        <f>IF($N66="","",INDEX(작업!F$6:F$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="F66" s="24">
+        <f>IF($N66="","",INDEX(작업!G$6:G$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="G66" s="40">
+        <f>IF($N66="","",INDEX(작업!H$6:H$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="H66" s="40">
+        <f>IF($N66="","",INDEX(작업!I$6:I$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="I66" s="25">
+        <f>IF($N66="","",INDEX(작업!J$6:J$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="J66" s="24">
+        <f>IF($N66="","",INDEX(작업!K$6:K$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="K66" s="39">
+        <f>IF($N66="","",INDEX(작업!L$6:L$105,$N66))</f>
+        <v/>
+      </c>
+      <c r="N66">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N66)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="24">
+        <f>IF($N67="","",INDEX(작업!B$6:B$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="C67" s="39">
+        <f>IF($N67="","",INDEX(작업!D$6:D$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="D67" s="24">
+        <f>IF($N67="","",INDEX(작업!E$6:E$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="E67" s="24">
+        <f>IF($N67="","",INDEX(작업!F$6:F$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="F67" s="24">
+        <f>IF($N67="","",INDEX(작업!G$6:G$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="G67" s="40">
+        <f>IF($N67="","",INDEX(작업!H$6:H$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="H67" s="40">
+        <f>IF($N67="","",INDEX(작업!I$6:I$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="I67" s="25">
+        <f>IF($N67="","",INDEX(작업!J$6:J$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="J67" s="24">
+        <f>IF($N67="","",INDEX(작업!K$6:K$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="K67" s="39">
+        <f>IF($N67="","",INDEX(작업!L$6:L$105,$N67))</f>
+        <v/>
+      </c>
+      <c r="N67">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N67)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="24">
+        <f>IF($N68="","",INDEX(작업!B$6:B$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="C68" s="39">
+        <f>IF($N68="","",INDEX(작업!D$6:D$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="D68" s="24">
+        <f>IF($N68="","",INDEX(작업!E$6:E$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="E68" s="24">
+        <f>IF($N68="","",INDEX(작업!F$6:F$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="F68" s="24">
+        <f>IF($N68="","",INDEX(작업!G$6:G$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="G68" s="40">
+        <f>IF($N68="","",INDEX(작업!H$6:H$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="H68" s="40">
+        <f>IF($N68="","",INDEX(작업!I$6:I$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="I68" s="25">
+        <f>IF($N68="","",INDEX(작업!J$6:J$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="J68" s="24">
+        <f>IF($N68="","",INDEX(작업!K$6:K$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="K68" s="39">
+        <f>IF($N68="","",INDEX(작업!L$6:L$105,$N68))</f>
+        <v/>
+      </c>
+      <c r="N68">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N68)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="24">
+        <f>IF($N69="","",INDEX(작업!B$6:B$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="C69" s="39">
+        <f>IF($N69="","",INDEX(작업!D$6:D$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="D69" s="24">
+        <f>IF($N69="","",INDEX(작업!E$6:E$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="E69" s="24">
+        <f>IF($N69="","",INDEX(작업!F$6:F$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="F69" s="24">
+        <f>IF($N69="","",INDEX(작업!G$6:G$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="G69" s="40">
+        <f>IF($N69="","",INDEX(작업!H$6:H$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="H69" s="40">
+        <f>IF($N69="","",INDEX(작업!I$6:I$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="I69" s="25">
+        <f>IF($N69="","",INDEX(작업!J$6:J$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="J69" s="24">
+        <f>IF($N69="","",INDEX(작업!K$6:K$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="K69" s="39">
+        <f>IF($N69="","",INDEX(작업!L$6:L$105,$N69))</f>
+        <v/>
+      </c>
+      <c r="N69">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N69)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="24">
+        <f>IF($N70="","",INDEX(작업!B$6:B$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="C70" s="39">
+        <f>IF($N70="","",INDEX(작업!D$6:D$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="D70" s="24">
+        <f>IF($N70="","",INDEX(작업!E$6:E$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="E70" s="24">
+        <f>IF($N70="","",INDEX(작업!F$6:F$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="F70" s="24">
+        <f>IF($N70="","",INDEX(작업!G$6:G$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="G70" s="40">
+        <f>IF($N70="","",INDEX(작업!H$6:H$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="H70" s="40">
+        <f>IF($N70="","",INDEX(작업!I$6:I$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="I70" s="25">
+        <f>IF($N70="","",INDEX(작업!J$6:J$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="J70" s="24">
+        <f>IF($N70="","",INDEX(작업!K$6:K$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="K70" s="39">
+        <f>IF($N70="","",INDEX(작업!L$6:L$105,$N70))</f>
+        <v/>
+      </c>
+      <c r="N70">
+        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N70)),""))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:C7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"계획"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"진행중"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"완료"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"보류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"지연"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:F70">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"계획"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"진행중"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2">
+      <formula>"완료"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="3">
+      <formula>"보류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4">
+      <formula>"지연"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I70">
+    <cfRule type="dataBar" priority="11">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="002E75B6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11:J70">
+    <cfRule type="expression" priority="12" dxfId="4">
+      <formula>AND($B11&lt;&gt;"",$F11&lt;&gt;"완료",ISNUMBER($J11),$J11&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="6">
+      <formula>AND($B11&lt;&gt;"",$F11&lt;&gt;"완료",ISNUMBER($J11),$J11&gt;=0,$J11&lt;=7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=프로젝트ID목록</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5756,12 +8594,12 @@
           <t>📊 간트차트 (주 단위 타임라인)</t>
         </is>
       </c>
-      <c r="E2" s="41" t="inlineStr">
+      <c r="E2" s="46" t="inlineStr">
         <is>
           <t>기준일:</t>
         </is>
       </c>
-      <c r="F2" s="42" t="n">
+      <c r="F2" s="47" t="n">
         <v>46146</v>
       </c>
     </row>
@@ -5793,107 +8631,107 @@
           <t>마감일</t>
         </is>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="48">
         <f>$F$2+0</f>
         <v/>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="48">
         <f>$F$2+7</f>
         <v/>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="48">
         <f>$F$2+14</f>
         <v/>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="48">
         <f>$F$2+21</f>
         <v/>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="48">
         <f>$F$2+28</f>
         <v/>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="48">
         <f>$F$2+35</f>
         <v/>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="48">
         <f>$F$2+42</f>
         <v/>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="48">
         <f>$F$2+49</f>
         <v/>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="48">
         <f>$F$2+56</f>
         <v/>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="48">
         <f>$F$2+63</f>
         <v/>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="48">
         <f>$F$2+70</f>
         <v/>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="48">
         <f>$F$2+77</f>
         <v/>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="48">
         <f>$F$2+84</f>
         <v/>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="48">
         <f>$F$2+91</f>
         <v/>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="48">
         <f>$F$2+98</f>
         <v/>
       </c>
-      <c r="U5" s="43">
+      <c r="U5" s="48">
         <f>$F$2+105</f>
         <v/>
       </c>
-      <c r="V5" s="43">
+      <c r="V5" s="48">
         <f>$F$2+112</f>
         <v/>
       </c>
-      <c r="W5" s="43">
+      <c r="W5" s="48">
         <f>$F$2+119</f>
         <v/>
       </c>
-      <c r="X5" s="43">
+      <c r="X5" s="48">
         <f>$F$2+126</f>
         <v/>
       </c>
-      <c r="Y5" s="43">
+      <c r="Y5" s="48">
         <f>$F$2+133</f>
         <v/>
       </c>
-      <c r="Z5" s="43">
+      <c r="Z5" s="48">
         <f>$F$2+140</f>
         <v/>
       </c>
-      <c r="AA5" s="43">
+      <c r="AA5" s="48">
         <f>$F$2+147</f>
         <v/>
       </c>
-      <c r="AB5" s="43">
+      <c r="AB5" s="48">
         <f>$F$2+154</f>
         <v/>
       </c>
-      <c r="AC5" s="43">
+      <c r="AC5" s="48">
         <f>$F$2+161</f>
         <v/>
       </c>
-      <c r="AD5" s="43">
+      <c r="AD5" s="48">
         <f>$F$2+168</f>
         <v/>
       </c>
-      <c r="AE5" s="43">
+      <c r="AE5" s="48">
         <f>$F$2+175</f>
         <v/>
       </c>
@@ -5915,32 +8753,32 @@
         <f>IF(프로젝트!$C6="","",프로젝트!$I6)</f>
         <v/>
       </c>
-      <c r="F6" s="44" t="n"/>
-      <c r="G6" s="44" t="n"/>
-      <c r="H6" s="44" t="n"/>
-      <c r="I6" s="44" t="n"/>
-      <c r="J6" s="44" t="n"/>
-      <c r="K6" s="44" t="n"/>
-      <c r="L6" s="44" t="n"/>
-      <c r="M6" s="44" t="n"/>
-      <c r="N6" s="44" t="n"/>
-      <c r="O6" s="44" t="n"/>
-      <c r="P6" s="44" t="n"/>
-      <c r="Q6" s="44" t="n"/>
-      <c r="R6" s="44" t="n"/>
-      <c r="S6" s="44" t="n"/>
-      <c r="T6" s="44" t="n"/>
-      <c r="U6" s="44" t="n"/>
-      <c r="V6" s="44" t="n"/>
-      <c r="W6" s="44" t="n"/>
-      <c r="X6" s="44" t="n"/>
-      <c r="Y6" s="44" t="n"/>
-      <c r="Z6" s="44" t="n"/>
-      <c r="AA6" s="44" t="n"/>
-      <c r="AB6" s="44" t="n"/>
-      <c r="AC6" s="44" t="n"/>
-      <c r="AD6" s="44" t="n"/>
-      <c r="AE6" s="44" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="n"/>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="49" t="n"/>
+      <c r="M6" s="49" t="n"/>
+      <c r="N6" s="49" t="n"/>
+      <c r="O6" s="49" t="n"/>
+      <c r="P6" s="49" t="n"/>
+      <c r="Q6" s="49" t="n"/>
+      <c r="R6" s="49" t="n"/>
+      <c r="S6" s="49" t="n"/>
+      <c r="T6" s="49" t="n"/>
+      <c r="U6" s="49" t="n"/>
+      <c r="V6" s="49" t="n"/>
+      <c r="W6" s="49" t="n"/>
+      <c r="X6" s="49" t="n"/>
+      <c r="Y6" s="49" t="n"/>
+      <c r="Z6" s="49" t="n"/>
+      <c r="AA6" s="49" t="n"/>
+      <c r="AB6" s="49" t="n"/>
+      <c r="AC6" s="49" t="n"/>
+      <c r="AD6" s="49" t="n"/>
+      <c r="AE6" s="49" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="39">
@@ -5959,32 +8797,32 @@
         <f>IF(프로젝트!$C7="","",프로젝트!$I7)</f>
         <v/>
       </c>
-      <c r="F7" s="44" t="n"/>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="44" t="n"/>
-      <c r="I7" s="44" t="n"/>
-      <c r="J7" s="44" t="n"/>
-      <c r="K7" s="44" t="n"/>
-      <c r="L7" s="44" t="n"/>
-      <c r="M7" s="44" t="n"/>
-      <c r="N7" s="44" t="n"/>
-      <c r="O7" s="44" t="n"/>
-      <c r="P7" s="44" t="n"/>
-      <c r="Q7" s="44" t="n"/>
-      <c r="R7" s="44" t="n"/>
-      <c r="S7" s="44" t="n"/>
-      <c r="T7" s="44" t="n"/>
-      <c r="U7" s="44" t="n"/>
-      <c r="V7" s="44" t="n"/>
-      <c r="W7" s="44" t="n"/>
-      <c r="X7" s="44" t="n"/>
-      <c r="Y7" s="44" t="n"/>
-      <c r="Z7" s="44" t="n"/>
-      <c r="AA7" s="44" t="n"/>
-      <c r="AB7" s="44" t="n"/>
-      <c r="AC7" s="44" t="n"/>
-      <c r="AD7" s="44" t="n"/>
-      <c r="AE7" s="44" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+      <c r="M7" s="49" t="n"/>
+      <c r="N7" s="49" t="n"/>
+      <c r="O7" s="49" t="n"/>
+      <c r="P7" s="49" t="n"/>
+      <c r="Q7" s="49" t="n"/>
+      <c r="R7" s="49" t="n"/>
+      <c r="S7" s="49" t="n"/>
+      <c r="T7" s="49" t="n"/>
+      <c r="U7" s="49" t="n"/>
+      <c r="V7" s="49" t="n"/>
+      <c r="W7" s="49" t="n"/>
+      <c r="X7" s="49" t="n"/>
+      <c r="Y7" s="49" t="n"/>
+      <c r="Z7" s="49" t="n"/>
+      <c r="AA7" s="49" t="n"/>
+      <c r="AB7" s="49" t="n"/>
+      <c r="AC7" s="49" t="n"/>
+      <c r="AD7" s="49" t="n"/>
+      <c r="AE7" s="49" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="39">
@@ -6003,32 +8841,32 @@
         <f>IF(프로젝트!$C8="","",프로젝트!$I8)</f>
         <v/>
       </c>
-      <c r="F8" s="44" t="n"/>
-      <c r="G8" s="44" t="n"/>
-      <c r="H8" s="44" t="n"/>
-      <c r="I8" s="44" t="n"/>
-      <c r="J8" s="44" t="n"/>
-      <c r="K8" s="44" t="n"/>
-      <c r="L8" s="44" t="n"/>
-      <c r="M8" s="44" t="n"/>
-      <c r="N8" s="44" t="n"/>
-      <c r="O8" s="44" t="n"/>
-      <c r="P8" s="44" t="n"/>
-      <c r="Q8" s="44" t="n"/>
-      <c r="R8" s="44" t="n"/>
-      <c r="S8" s="44" t="n"/>
-      <c r="T8" s="44" t="n"/>
-      <c r="U8" s="44" t="n"/>
-      <c r="V8" s="44" t="n"/>
-      <c r="W8" s="44" t="n"/>
-      <c r="X8" s="44" t="n"/>
-      <c r="Y8" s="44" t="n"/>
-      <c r="Z8" s="44" t="n"/>
-      <c r="AA8" s="44" t="n"/>
-      <c r="AB8" s="44" t="n"/>
-      <c r="AC8" s="44" t="n"/>
-      <c r="AD8" s="44" t="n"/>
-      <c r="AE8" s="44" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="49" t="n"/>
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="49" t="n"/>
+      <c r="P8" s="49" t="n"/>
+      <c r="Q8" s="49" t="n"/>
+      <c r="R8" s="49" t="n"/>
+      <c r="S8" s="49" t="n"/>
+      <c r="T8" s="49" t="n"/>
+      <c r="U8" s="49" t="n"/>
+      <c r="V8" s="49" t="n"/>
+      <c r="W8" s="49" t="n"/>
+      <c r="X8" s="49" t="n"/>
+      <c r="Y8" s="49" t="n"/>
+      <c r="Z8" s="49" t="n"/>
+      <c r="AA8" s="49" t="n"/>
+      <c r="AB8" s="49" t="n"/>
+      <c r="AC8" s="49" t="n"/>
+      <c r="AD8" s="49" t="n"/>
+      <c r="AE8" s="49" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="39">
@@ -6047,32 +8885,32 @@
         <f>IF(프로젝트!$C9="","",프로젝트!$I9)</f>
         <v/>
       </c>
-      <c r="F9" s="44" t="n"/>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="44" t="n"/>
-      <c r="I9" s="44" t="n"/>
-      <c r="J9" s="44" t="n"/>
-      <c r="K9" s="44" t="n"/>
-      <c r="L9" s="44" t="n"/>
-      <c r="M9" s="44" t="n"/>
-      <c r="N9" s="44" t="n"/>
-      <c r="O9" s="44" t="n"/>
-      <c r="P9" s="44" t="n"/>
-      <c r="Q9" s="44" t="n"/>
-      <c r="R9" s="44" t="n"/>
-      <c r="S9" s="44" t="n"/>
-      <c r="T9" s="44" t="n"/>
-      <c r="U9" s="44" t="n"/>
-      <c r="V9" s="44" t="n"/>
-      <c r="W9" s="44" t="n"/>
-      <c r="X9" s="44" t="n"/>
-      <c r="Y9" s="44" t="n"/>
-      <c r="Z9" s="44" t="n"/>
-      <c r="AA9" s="44" t="n"/>
-      <c r="AB9" s="44" t="n"/>
-      <c r="AC9" s="44" t="n"/>
-      <c r="AD9" s="44" t="n"/>
-      <c r="AE9" s="44" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="49" t="n"/>
+      <c r="I9" s="49" t="n"/>
+      <c r="J9" s="49" t="n"/>
+      <c r="K9" s="49" t="n"/>
+      <c r="L9" s="49" t="n"/>
+      <c r="M9" s="49" t="n"/>
+      <c r="N9" s="49" t="n"/>
+      <c r="O9" s="49" t="n"/>
+      <c r="P9" s="49" t="n"/>
+      <c r="Q9" s="49" t="n"/>
+      <c r="R9" s="49" t="n"/>
+      <c r="S9" s="49" t="n"/>
+      <c r="T9" s="49" t="n"/>
+      <c r="U9" s="49" t="n"/>
+      <c r="V9" s="49" t="n"/>
+      <c r="W9" s="49" t="n"/>
+      <c r="X9" s="49" t="n"/>
+      <c r="Y9" s="49" t="n"/>
+      <c r="Z9" s="49" t="n"/>
+      <c r="AA9" s="49" t="n"/>
+      <c r="AB9" s="49" t="n"/>
+      <c r="AC9" s="49" t="n"/>
+      <c r="AD9" s="49" t="n"/>
+      <c r="AE9" s="49" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="39">
@@ -6091,32 +8929,32 @@
         <f>IF(프로젝트!$C10="","",프로젝트!$I10)</f>
         <v/>
       </c>
-      <c r="F10" s="44" t="n"/>
-      <c r="G10" s="44" t="n"/>
-      <c r="H10" s="44" t="n"/>
-      <c r="I10" s="44" t="n"/>
-      <c r="J10" s="44" t="n"/>
-      <c r="K10" s="44" t="n"/>
-      <c r="L10" s="44" t="n"/>
-      <c r="M10" s="44" t="n"/>
-      <c r="N10" s="44" t="n"/>
-      <c r="O10" s="44" t="n"/>
-      <c r="P10" s="44" t="n"/>
-      <c r="Q10" s="44" t="n"/>
-      <c r="R10" s="44" t="n"/>
-      <c r="S10" s="44" t="n"/>
-      <c r="T10" s="44" t="n"/>
-      <c r="U10" s="44" t="n"/>
-      <c r="V10" s="44" t="n"/>
-      <c r="W10" s="44" t="n"/>
-      <c r="X10" s="44" t="n"/>
-      <c r="Y10" s="44" t="n"/>
-      <c r="Z10" s="44" t="n"/>
-      <c r="AA10" s="44" t="n"/>
-      <c r="AB10" s="44" t="n"/>
-      <c r="AC10" s="44" t="n"/>
-      <c r="AD10" s="44" t="n"/>
-      <c r="AE10" s="44" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="49" t="n"/>
+      <c r="K10" s="49" t="n"/>
+      <c r="L10" s="49" t="n"/>
+      <c r="M10" s="49" t="n"/>
+      <c r="N10" s="49" t="n"/>
+      <c r="O10" s="49" t="n"/>
+      <c r="P10" s="49" t="n"/>
+      <c r="Q10" s="49" t="n"/>
+      <c r="R10" s="49" t="n"/>
+      <c r="S10" s="49" t="n"/>
+      <c r="T10" s="49" t="n"/>
+      <c r="U10" s="49" t="n"/>
+      <c r="V10" s="49" t="n"/>
+      <c r="W10" s="49" t="n"/>
+      <c r="X10" s="49" t="n"/>
+      <c r="Y10" s="49" t="n"/>
+      <c r="Z10" s="49" t="n"/>
+      <c r="AA10" s="49" t="n"/>
+      <c r="AB10" s="49" t="n"/>
+      <c r="AC10" s="49" t="n"/>
+      <c r="AD10" s="49" t="n"/>
+      <c r="AE10" s="49" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="39">
@@ -6135,32 +8973,32 @@
         <f>IF(프로젝트!$C11="","",프로젝트!$I11)</f>
         <v/>
       </c>
-      <c r="F11" s="44" t="n"/>
-      <c r="G11" s="44" t="n"/>
-      <c r="H11" s="44" t="n"/>
-      <c r="I11" s="44" t="n"/>
-      <c r="J11" s="44" t="n"/>
-      <c r="K11" s="44" t="n"/>
-      <c r="L11" s="44" t="n"/>
-      <c r="M11" s="44" t="n"/>
-      <c r="N11" s="44" t="n"/>
-      <c r="O11" s="44" t="n"/>
-      <c r="P11" s="44" t="n"/>
-      <c r="Q11" s="44" t="n"/>
-      <c r="R11" s="44" t="n"/>
-      <c r="S11" s="44" t="n"/>
-      <c r="T11" s="44" t="n"/>
-      <c r="U11" s="44" t="n"/>
-      <c r="V11" s="44" t="n"/>
-      <c r="W11" s="44" t="n"/>
-      <c r="X11" s="44" t="n"/>
-      <c r="Y11" s="44" t="n"/>
-      <c r="Z11" s="44" t="n"/>
-      <c r="AA11" s="44" t="n"/>
-      <c r="AB11" s="44" t="n"/>
-      <c r="AC11" s="44" t="n"/>
-      <c r="AD11" s="44" t="n"/>
-      <c r="AE11" s="44" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="49" t="n"/>
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="49" t="n"/>
+      <c r="M11" s="49" t="n"/>
+      <c r="N11" s="49" t="n"/>
+      <c r="O11" s="49" t="n"/>
+      <c r="P11" s="49" t="n"/>
+      <c r="Q11" s="49" t="n"/>
+      <c r="R11" s="49" t="n"/>
+      <c r="S11" s="49" t="n"/>
+      <c r="T11" s="49" t="n"/>
+      <c r="U11" s="49" t="n"/>
+      <c r="V11" s="49" t="n"/>
+      <c r="W11" s="49" t="n"/>
+      <c r="X11" s="49" t="n"/>
+      <c r="Y11" s="49" t="n"/>
+      <c r="Z11" s="49" t="n"/>
+      <c r="AA11" s="49" t="n"/>
+      <c r="AB11" s="49" t="n"/>
+      <c r="AC11" s="49" t="n"/>
+      <c r="AD11" s="49" t="n"/>
+      <c r="AE11" s="49" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="39">
@@ -6179,32 +9017,32 @@
         <f>IF(프로젝트!$C12="","",프로젝트!$I12)</f>
         <v/>
       </c>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
-      <c r="I12" s="44" t="n"/>
-      <c r="J12" s="44" t="n"/>
-      <c r="K12" s="44" t="n"/>
-      <c r="L12" s="44" t="n"/>
-      <c r="M12" s="44" t="n"/>
-      <c r="N12" s="44" t="n"/>
-      <c r="O12" s="44" t="n"/>
-      <c r="P12" s="44" t="n"/>
-      <c r="Q12" s="44" t="n"/>
-      <c r="R12" s="44" t="n"/>
-      <c r="S12" s="44" t="n"/>
-      <c r="T12" s="44" t="n"/>
-      <c r="U12" s="44" t="n"/>
-      <c r="V12" s="44" t="n"/>
-      <c r="W12" s="44" t="n"/>
-      <c r="X12" s="44" t="n"/>
-      <c r="Y12" s="44" t="n"/>
-      <c r="Z12" s="44" t="n"/>
-      <c r="AA12" s="44" t="n"/>
-      <c r="AB12" s="44" t="n"/>
-      <c r="AC12" s="44" t="n"/>
-      <c r="AD12" s="44" t="n"/>
-      <c r="AE12" s="44" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="49" t="n"/>
+      <c r="K12" s="49" t="n"/>
+      <c r="L12" s="49" t="n"/>
+      <c r="M12" s="49" t="n"/>
+      <c r="N12" s="49" t="n"/>
+      <c r="O12" s="49" t="n"/>
+      <c r="P12" s="49" t="n"/>
+      <c r="Q12" s="49" t="n"/>
+      <c r="R12" s="49" t="n"/>
+      <c r="S12" s="49" t="n"/>
+      <c r="T12" s="49" t="n"/>
+      <c r="U12" s="49" t="n"/>
+      <c r="V12" s="49" t="n"/>
+      <c r="W12" s="49" t="n"/>
+      <c r="X12" s="49" t="n"/>
+      <c r="Y12" s="49" t="n"/>
+      <c r="Z12" s="49" t="n"/>
+      <c r="AA12" s="49" t="n"/>
+      <c r="AB12" s="49" t="n"/>
+      <c r="AC12" s="49" t="n"/>
+      <c r="AD12" s="49" t="n"/>
+      <c r="AE12" s="49" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="39">
@@ -6223,32 +9061,32 @@
         <f>IF(프로젝트!$C13="","",프로젝트!$I13)</f>
         <v/>
       </c>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
-      <c r="I13" s="44" t="n"/>
-      <c r="J13" s="44" t="n"/>
-      <c r="K13" s="44" t="n"/>
-      <c r="L13" s="44" t="n"/>
-      <c r="M13" s="44" t="n"/>
-      <c r="N13" s="44" t="n"/>
-      <c r="O13" s="44" t="n"/>
-      <c r="P13" s="44" t="n"/>
-      <c r="Q13" s="44" t="n"/>
-      <c r="R13" s="44" t="n"/>
-      <c r="S13" s="44" t="n"/>
-      <c r="T13" s="44" t="n"/>
-      <c r="U13" s="44" t="n"/>
-      <c r="V13" s="44" t="n"/>
-      <c r="W13" s="44" t="n"/>
-      <c r="X13" s="44" t="n"/>
-      <c r="Y13" s="44" t="n"/>
-      <c r="Z13" s="44" t="n"/>
-      <c r="AA13" s="44" t="n"/>
-      <c r="AB13" s="44" t="n"/>
-      <c r="AC13" s="44" t="n"/>
-      <c r="AD13" s="44" t="n"/>
-      <c r="AE13" s="44" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="49" t="n"/>
+      <c r="K13" s="49" t="n"/>
+      <c r="L13" s="49" t="n"/>
+      <c r="M13" s="49" t="n"/>
+      <c r="N13" s="49" t="n"/>
+      <c r="O13" s="49" t="n"/>
+      <c r="P13" s="49" t="n"/>
+      <c r="Q13" s="49" t="n"/>
+      <c r="R13" s="49" t="n"/>
+      <c r="S13" s="49" t="n"/>
+      <c r="T13" s="49" t="n"/>
+      <c r="U13" s="49" t="n"/>
+      <c r="V13" s="49" t="n"/>
+      <c r="W13" s="49" t="n"/>
+      <c r="X13" s="49" t="n"/>
+      <c r="Y13" s="49" t="n"/>
+      <c r="Z13" s="49" t="n"/>
+      <c r="AA13" s="49" t="n"/>
+      <c r="AB13" s="49" t="n"/>
+      <c r="AC13" s="49" t="n"/>
+      <c r="AD13" s="49" t="n"/>
+      <c r="AE13" s="49" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="39">
@@ -6267,32 +9105,32 @@
         <f>IF(프로젝트!$C14="","",프로젝트!$I14)</f>
         <v/>
       </c>
-      <c r="F14" s="44" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="44" t="n"/>
-      <c r="I14" s="44" t="n"/>
-      <c r="J14" s="44" t="n"/>
-      <c r="K14" s="44" t="n"/>
-      <c r="L14" s="44" t="n"/>
-      <c r="M14" s="44" t="n"/>
-      <c r="N14" s="44" t="n"/>
-      <c r="O14" s="44" t="n"/>
-      <c r="P14" s="44" t="n"/>
-      <c r="Q14" s="44" t="n"/>
-      <c r="R14" s="44" t="n"/>
-      <c r="S14" s="44" t="n"/>
-      <c r="T14" s="44" t="n"/>
-      <c r="U14" s="44" t="n"/>
-      <c r="V14" s="44" t="n"/>
-      <c r="W14" s="44" t="n"/>
-      <c r="X14" s="44" t="n"/>
-      <c r="Y14" s="44" t="n"/>
-      <c r="Z14" s="44" t="n"/>
-      <c r="AA14" s="44" t="n"/>
-      <c r="AB14" s="44" t="n"/>
-      <c r="AC14" s="44" t="n"/>
-      <c r="AD14" s="44" t="n"/>
-      <c r="AE14" s="44" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="49" t="n"/>
+      <c r="K14" s="49" t="n"/>
+      <c r="L14" s="49" t="n"/>
+      <c r="M14" s="49" t="n"/>
+      <c r="N14" s="49" t="n"/>
+      <c r="O14" s="49" t="n"/>
+      <c r="P14" s="49" t="n"/>
+      <c r="Q14" s="49" t="n"/>
+      <c r="R14" s="49" t="n"/>
+      <c r="S14" s="49" t="n"/>
+      <c r="T14" s="49" t="n"/>
+      <c r="U14" s="49" t="n"/>
+      <c r="V14" s="49" t="n"/>
+      <c r="W14" s="49" t="n"/>
+      <c r="X14" s="49" t="n"/>
+      <c r="Y14" s="49" t="n"/>
+      <c r="Z14" s="49" t="n"/>
+      <c r="AA14" s="49" t="n"/>
+      <c r="AB14" s="49" t="n"/>
+      <c r="AC14" s="49" t="n"/>
+      <c r="AD14" s="49" t="n"/>
+      <c r="AE14" s="49" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="39">
@@ -6311,32 +9149,32 @@
         <f>IF(프로젝트!$C15="","",프로젝트!$I15)</f>
         <v/>
       </c>
-      <c r="F15" s="44" t="n"/>
-      <c r="G15" s="44" t="n"/>
-      <c r="H15" s="44" t="n"/>
-      <c r="I15" s="44" t="n"/>
-      <c r="J15" s="44" t="n"/>
-      <c r="K15" s="44" t="n"/>
-      <c r="L15" s="44" t="n"/>
-      <c r="M15" s="44" t="n"/>
-      <c r="N15" s="44" t="n"/>
-      <c r="O15" s="44" t="n"/>
-      <c r="P15" s="44" t="n"/>
-      <c r="Q15" s="44" t="n"/>
-      <c r="R15" s="44" t="n"/>
-      <c r="S15" s="44" t="n"/>
-      <c r="T15" s="44" t="n"/>
-      <c r="U15" s="44" t="n"/>
-      <c r="V15" s="44" t="n"/>
-      <c r="W15" s="44" t="n"/>
-      <c r="X15" s="44" t="n"/>
-      <c r="Y15" s="44" t="n"/>
-      <c r="Z15" s="44" t="n"/>
-      <c r="AA15" s="44" t="n"/>
-      <c r="AB15" s="44" t="n"/>
-      <c r="AC15" s="44" t="n"/>
-      <c r="AD15" s="44" t="n"/>
-      <c r="AE15" s="44" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49" t="n"/>
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="49" t="n"/>
+      <c r="M15" s="49" t="n"/>
+      <c r="N15" s="49" t="n"/>
+      <c r="O15" s="49" t="n"/>
+      <c r="P15" s="49" t="n"/>
+      <c r="Q15" s="49" t="n"/>
+      <c r="R15" s="49" t="n"/>
+      <c r="S15" s="49" t="n"/>
+      <c r="T15" s="49" t="n"/>
+      <c r="U15" s="49" t="n"/>
+      <c r="V15" s="49" t="n"/>
+      <c r="W15" s="49" t="n"/>
+      <c r="X15" s="49" t="n"/>
+      <c r="Y15" s="49" t="n"/>
+      <c r="Z15" s="49" t="n"/>
+      <c r="AA15" s="49" t="n"/>
+      <c r="AB15" s="49" t="n"/>
+      <c r="AC15" s="49" t="n"/>
+      <c r="AD15" s="49" t="n"/>
+      <c r="AE15" s="49" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="39">
@@ -6355,32 +9193,32 @@
         <f>IF(프로젝트!$C16="","",프로젝트!$I16)</f>
         <v/>
       </c>
-      <c r="F16" s="44" t="n"/>
-      <c r="G16" s="44" t="n"/>
-      <c r="H16" s="44" t="n"/>
-      <c r="I16" s="44" t="n"/>
-      <c r="J16" s="44" t="n"/>
-      <c r="K16" s="44" t="n"/>
-      <c r="L16" s="44" t="n"/>
-      <c r="M16" s="44" t="n"/>
-      <c r="N16" s="44" t="n"/>
-      <c r="O16" s="44" t="n"/>
-      <c r="P16" s="44" t="n"/>
-      <c r="Q16" s="44" t="n"/>
-      <c r="R16" s="44" t="n"/>
-      <c r="S16" s="44" t="n"/>
-      <c r="T16" s="44" t="n"/>
-      <c r="U16" s="44" t="n"/>
-      <c r="V16" s="44" t="n"/>
-      <c r="W16" s="44" t="n"/>
-      <c r="X16" s="44" t="n"/>
-      <c r="Y16" s="44" t="n"/>
-      <c r="Z16" s="44" t="n"/>
-      <c r="AA16" s="44" t="n"/>
-      <c r="AB16" s="44" t="n"/>
-      <c r="AC16" s="44" t="n"/>
-      <c r="AD16" s="44" t="n"/>
-      <c r="AE16" s="44" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
+      <c r="M16" s="49" t="n"/>
+      <c r="N16" s="49" t="n"/>
+      <c r="O16" s="49" t="n"/>
+      <c r="P16" s="49" t="n"/>
+      <c r="Q16" s="49" t="n"/>
+      <c r="R16" s="49" t="n"/>
+      <c r="S16" s="49" t="n"/>
+      <c r="T16" s="49" t="n"/>
+      <c r="U16" s="49" t="n"/>
+      <c r="V16" s="49" t="n"/>
+      <c r="W16" s="49" t="n"/>
+      <c r="X16" s="49" t="n"/>
+      <c r="Y16" s="49" t="n"/>
+      <c r="Z16" s="49" t="n"/>
+      <c r="AA16" s="49" t="n"/>
+      <c r="AB16" s="49" t="n"/>
+      <c r="AC16" s="49" t="n"/>
+      <c r="AD16" s="49" t="n"/>
+      <c r="AE16" s="49" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="39">
@@ -6399,32 +9237,32 @@
         <f>IF(프로젝트!$C17="","",프로젝트!$I17)</f>
         <v/>
       </c>
-      <c r="F17" s="44" t="n"/>
-      <c r="G17" s="44" t="n"/>
-      <c r="H17" s="44" t="n"/>
-      <c r="I17" s="44" t="n"/>
-      <c r="J17" s="44" t="n"/>
-      <c r="K17" s="44" t="n"/>
-      <c r="L17" s="44" t="n"/>
-      <c r="M17" s="44" t="n"/>
-      <c r="N17" s="44" t="n"/>
-      <c r="O17" s="44" t="n"/>
-      <c r="P17" s="44" t="n"/>
-      <c r="Q17" s="44" t="n"/>
-      <c r="R17" s="44" t="n"/>
-      <c r="S17" s="44" t="n"/>
-      <c r="T17" s="44" t="n"/>
-      <c r="U17" s="44" t="n"/>
-      <c r="V17" s="44" t="n"/>
-      <c r="W17" s="44" t="n"/>
-      <c r="X17" s="44" t="n"/>
-      <c r="Y17" s="44" t="n"/>
-      <c r="Z17" s="44" t="n"/>
-      <c r="AA17" s="44" t="n"/>
-      <c r="AB17" s="44" t="n"/>
-      <c r="AC17" s="44" t="n"/>
-      <c r="AD17" s="44" t="n"/>
-      <c r="AE17" s="44" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="49" t="n"/>
+      <c r="K17" s="49" t="n"/>
+      <c r="L17" s="49" t="n"/>
+      <c r="M17" s="49" t="n"/>
+      <c r="N17" s="49" t="n"/>
+      <c r="O17" s="49" t="n"/>
+      <c r="P17" s="49" t="n"/>
+      <c r="Q17" s="49" t="n"/>
+      <c r="R17" s="49" t="n"/>
+      <c r="S17" s="49" t="n"/>
+      <c r="T17" s="49" t="n"/>
+      <c r="U17" s="49" t="n"/>
+      <c r="V17" s="49" t="n"/>
+      <c r="W17" s="49" t="n"/>
+      <c r="X17" s="49" t="n"/>
+      <c r="Y17" s="49" t="n"/>
+      <c r="Z17" s="49" t="n"/>
+      <c r="AA17" s="49" t="n"/>
+      <c r="AB17" s="49" t="n"/>
+      <c r="AC17" s="49" t="n"/>
+      <c r="AD17" s="49" t="n"/>
+      <c r="AE17" s="49" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="39">
@@ -6443,32 +9281,32 @@
         <f>IF(프로젝트!$C18="","",프로젝트!$I18)</f>
         <v/>
       </c>
-      <c r="F18" s="44" t="n"/>
-      <c r="G18" s="44" t="n"/>
-      <c r="H18" s="44" t="n"/>
-      <c r="I18" s="44" t="n"/>
-      <c r="J18" s="44" t="n"/>
-      <c r="K18" s="44" t="n"/>
-      <c r="L18" s="44" t="n"/>
-      <c r="M18" s="44" t="n"/>
-      <c r="N18" s="44" t="n"/>
-      <c r="O18" s="44" t="n"/>
-      <c r="P18" s="44" t="n"/>
-      <c r="Q18" s="44" t="n"/>
-      <c r="R18" s="44" t="n"/>
-      <c r="S18" s="44" t="n"/>
-      <c r="T18" s="44" t="n"/>
-      <c r="U18" s="44" t="n"/>
-      <c r="V18" s="44" t="n"/>
-      <c r="W18" s="44" t="n"/>
-      <c r="X18" s="44" t="n"/>
-      <c r="Y18" s="44" t="n"/>
-      <c r="Z18" s="44" t="n"/>
-      <c r="AA18" s="44" t="n"/>
-      <c r="AB18" s="44" t="n"/>
-      <c r="AC18" s="44" t="n"/>
-      <c r="AD18" s="44" t="n"/>
-      <c r="AE18" s="44" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="49" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="49" t="n"/>
+      <c r="M18" s="49" t="n"/>
+      <c r="N18" s="49" t="n"/>
+      <c r="O18" s="49" t="n"/>
+      <c r="P18" s="49" t="n"/>
+      <c r="Q18" s="49" t="n"/>
+      <c r="R18" s="49" t="n"/>
+      <c r="S18" s="49" t="n"/>
+      <c r="T18" s="49" t="n"/>
+      <c r="U18" s="49" t="n"/>
+      <c r="V18" s="49" t="n"/>
+      <c r="W18" s="49" t="n"/>
+      <c r="X18" s="49" t="n"/>
+      <c r="Y18" s="49" t="n"/>
+      <c r="Z18" s="49" t="n"/>
+      <c r="AA18" s="49" t="n"/>
+      <c r="AB18" s="49" t="n"/>
+      <c r="AC18" s="49" t="n"/>
+      <c r="AD18" s="49" t="n"/>
+      <c r="AE18" s="49" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="39">
@@ -6487,32 +9325,32 @@
         <f>IF(프로젝트!$C19="","",프로젝트!$I19)</f>
         <v/>
       </c>
-      <c r="F19" s="44" t="n"/>
-      <c r="G19" s="44" t="n"/>
-      <c r="H19" s="44" t="n"/>
-      <c r="I19" s="44" t="n"/>
-      <c r="J19" s="44" t="n"/>
-      <c r="K19" s="44" t="n"/>
-      <c r="L19" s="44" t="n"/>
-      <c r="M19" s="44" t="n"/>
-      <c r="N19" s="44" t="n"/>
-      <c r="O19" s="44" t="n"/>
-      <c r="P19" s="44" t="n"/>
-      <c r="Q19" s="44" t="n"/>
-      <c r="R19" s="44" t="n"/>
-      <c r="S19" s="44" t="n"/>
-      <c r="T19" s="44" t="n"/>
-      <c r="U19" s="44" t="n"/>
-      <c r="V19" s="44" t="n"/>
-      <c r="W19" s="44" t="n"/>
-      <c r="X19" s="44" t="n"/>
-      <c r="Y19" s="44" t="n"/>
-      <c r="Z19" s="44" t="n"/>
-      <c r="AA19" s="44" t="n"/>
-      <c r="AB19" s="44" t="n"/>
-      <c r="AC19" s="44" t="n"/>
-      <c r="AD19" s="44" t="n"/>
-      <c r="AE19" s="44" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="49" t="n"/>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="49" t="n"/>
+      <c r="M19" s="49" t="n"/>
+      <c r="N19" s="49" t="n"/>
+      <c r="O19" s="49" t="n"/>
+      <c r="P19" s="49" t="n"/>
+      <c r="Q19" s="49" t="n"/>
+      <c r="R19" s="49" t="n"/>
+      <c r="S19" s="49" t="n"/>
+      <c r="T19" s="49" t="n"/>
+      <c r="U19" s="49" t="n"/>
+      <c r="V19" s="49" t="n"/>
+      <c r="W19" s="49" t="n"/>
+      <c r="X19" s="49" t="n"/>
+      <c r="Y19" s="49" t="n"/>
+      <c r="Z19" s="49" t="n"/>
+      <c r="AA19" s="49" t="n"/>
+      <c r="AB19" s="49" t="n"/>
+      <c r="AC19" s="49" t="n"/>
+      <c r="AD19" s="49" t="n"/>
+      <c r="AE19" s="49" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="39">
@@ -6531,32 +9369,32 @@
         <f>IF(프로젝트!$C20="","",프로젝트!$I20)</f>
         <v/>
       </c>
-      <c r="F20" s="44" t="n"/>
-      <c r="G20" s="44" t="n"/>
-      <c r="H20" s="44" t="n"/>
-      <c r="I20" s="44" t="n"/>
-      <c r="J20" s="44" t="n"/>
-      <c r="K20" s="44" t="n"/>
-      <c r="L20" s="44" t="n"/>
-      <c r="M20" s="44" t="n"/>
-      <c r="N20" s="44" t="n"/>
-      <c r="O20" s="44" t="n"/>
-      <c r="P20" s="44" t="n"/>
-      <c r="Q20" s="44" t="n"/>
-      <c r="R20" s="44" t="n"/>
-      <c r="S20" s="44" t="n"/>
-      <c r="T20" s="44" t="n"/>
-      <c r="U20" s="44" t="n"/>
-      <c r="V20" s="44" t="n"/>
-      <c r="W20" s="44" t="n"/>
-      <c r="X20" s="44" t="n"/>
-      <c r="Y20" s="44" t="n"/>
-      <c r="Z20" s="44" t="n"/>
-      <c r="AA20" s="44" t="n"/>
-      <c r="AB20" s="44" t="n"/>
-      <c r="AC20" s="44" t="n"/>
-      <c r="AD20" s="44" t="n"/>
-      <c r="AE20" s="44" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="49" t="n"/>
+      <c r="K20" s="49" t="n"/>
+      <c r="L20" s="49" t="n"/>
+      <c r="M20" s="49" t="n"/>
+      <c r="N20" s="49" t="n"/>
+      <c r="O20" s="49" t="n"/>
+      <c r="P20" s="49" t="n"/>
+      <c r="Q20" s="49" t="n"/>
+      <c r="R20" s="49" t="n"/>
+      <c r="S20" s="49" t="n"/>
+      <c r="T20" s="49" t="n"/>
+      <c r="U20" s="49" t="n"/>
+      <c r="V20" s="49" t="n"/>
+      <c r="W20" s="49" t="n"/>
+      <c r="X20" s="49" t="n"/>
+      <c r="Y20" s="49" t="n"/>
+      <c r="Z20" s="49" t="n"/>
+      <c r="AA20" s="49" t="n"/>
+      <c r="AB20" s="49" t="n"/>
+      <c r="AC20" s="49" t="n"/>
+      <c r="AD20" s="49" t="n"/>
+      <c r="AE20" s="49" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="39">
@@ -6575,32 +9413,32 @@
         <f>IF(프로젝트!$C21="","",프로젝트!$I21)</f>
         <v/>
       </c>
-      <c r="F21" s="44" t="n"/>
-      <c r="G21" s="44" t="n"/>
-      <c r="H21" s="44" t="n"/>
-      <c r="I21" s="44" t="n"/>
-      <c r="J21" s="44" t="n"/>
-      <c r="K21" s="44" t="n"/>
-      <c r="L21" s="44" t="n"/>
-      <c r="M21" s="44" t="n"/>
-      <c r="N21" s="44" t="n"/>
-      <c r="O21" s="44" t="n"/>
-      <c r="P21" s="44" t="n"/>
-      <c r="Q21" s="44" t="n"/>
-      <c r="R21" s="44" t="n"/>
-      <c r="S21" s="44" t="n"/>
-      <c r="T21" s="44" t="n"/>
-      <c r="U21" s="44" t="n"/>
-      <c r="V21" s="44" t="n"/>
-      <c r="W21" s="44" t="n"/>
-      <c r="X21" s="44" t="n"/>
-      <c r="Y21" s="44" t="n"/>
-      <c r="Z21" s="44" t="n"/>
-      <c r="AA21" s="44" t="n"/>
-      <c r="AB21" s="44" t="n"/>
-      <c r="AC21" s="44" t="n"/>
-      <c r="AD21" s="44" t="n"/>
-      <c r="AE21" s="44" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="49" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="49" t="n"/>
+      <c r="M21" s="49" t="n"/>
+      <c r="N21" s="49" t="n"/>
+      <c r="O21" s="49" t="n"/>
+      <c r="P21" s="49" t="n"/>
+      <c r="Q21" s="49" t="n"/>
+      <c r="R21" s="49" t="n"/>
+      <c r="S21" s="49" t="n"/>
+      <c r="T21" s="49" t="n"/>
+      <c r="U21" s="49" t="n"/>
+      <c r="V21" s="49" t="n"/>
+      <c r="W21" s="49" t="n"/>
+      <c r="X21" s="49" t="n"/>
+      <c r="Y21" s="49" t="n"/>
+      <c r="Z21" s="49" t="n"/>
+      <c r="AA21" s="49" t="n"/>
+      <c r="AB21" s="49" t="n"/>
+      <c r="AC21" s="49" t="n"/>
+      <c r="AD21" s="49" t="n"/>
+      <c r="AE21" s="49" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="39">
@@ -6619,32 +9457,32 @@
         <f>IF(프로젝트!$C22="","",프로젝트!$I22)</f>
         <v/>
       </c>
-      <c r="F22" s="44" t="n"/>
-      <c r="G22" s="44" t="n"/>
-      <c r="H22" s="44" t="n"/>
-      <c r="I22" s="44" t="n"/>
-      <c r="J22" s="44" t="n"/>
-      <c r="K22" s="44" t="n"/>
-      <c r="L22" s="44" t="n"/>
-      <c r="M22" s="44" t="n"/>
-      <c r="N22" s="44" t="n"/>
-      <c r="O22" s="44" t="n"/>
-      <c r="P22" s="44" t="n"/>
-      <c r="Q22" s="44" t="n"/>
-      <c r="R22" s="44" t="n"/>
-      <c r="S22" s="44" t="n"/>
-      <c r="T22" s="44" t="n"/>
-      <c r="U22" s="44" t="n"/>
-      <c r="V22" s="44" t="n"/>
-      <c r="W22" s="44" t="n"/>
-      <c r="X22" s="44" t="n"/>
-      <c r="Y22" s="44" t="n"/>
-      <c r="Z22" s="44" t="n"/>
-      <c r="AA22" s="44" t="n"/>
-      <c r="AB22" s="44" t="n"/>
-      <c r="AC22" s="44" t="n"/>
-      <c r="AD22" s="44" t="n"/>
-      <c r="AE22" s="44" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="49" t="n"/>
+      <c r="K22" s="49" t="n"/>
+      <c r="L22" s="49" t="n"/>
+      <c r="M22" s="49" t="n"/>
+      <c r="N22" s="49" t="n"/>
+      <c r="O22" s="49" t="n"/>
+      <c r="P22" s="49" t="n"/>
+      <c r="Q22" s="49" t="n"/>
+      <c r="R22" s="49" t="n"/>
+      <c r="S22" s="49" t="n"/>
+      <c r="T22" s="49" t="n"/>
+      <c r="U22" s="49" t="n"/>
+      <c r="V22" s="49" t="n"/>
+      <c r="W22" s="49" t="n"/>
+      <c r="X22" s="49" t="n"/>
+      <c r="Y22" s="49" t="n"/>
+      <c r="Z22" s="49" t="n"/>
+      <c r="AA22" s="49" t="n"/>
+      <c r="AB22" s="49" t="n"/>
+      <c r="AC22" s="49" t="n"/>
+      <c r="AD22" s="49" t="n"/>
+      <c r="AE22" s="49" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="39">
@@ -6663,32 +9501,32 @@
         <f>IF(프로젝트!$C23="","",프로젝트!$I23)</f>
         <v/>
       </c>
-      <c r="F23" s="44" t="n"/>
-      <c r="G23" s="44" t="n"/>
-      <c r="H23" s="44" t="n"/>
-      <c r="I23" s="44" t="n"/>
-      <c r="J23" s="44" t="n"/>
-      <c r="K23" s="44" t="n"/>
-      <c r="L23" s="44" t="n"/>
-      <c r="M23" s="44" t="n"/>
-      <c r="N23" s="44" t="n"/>
-      <c r="O23" s="44" t="n"/>
-      <c r="P23" s="44" t="n"/>
-      <c r="Q23" s="44" t="n"/>
-      <c r="R23" s="44" t="n"/>
-      <c r="S23" s="44" t="n"/>
-      <c r="T23" s="44" t="n"/>
-      <c r="U23" s="44" t="n"/>
-      <c r="V23" s="44" t="n"/>
-      <c r="W23" s="44" t="n"/>
-      <c r="X23" s="44" t="n"/>
-      <c r="Y23" s="44" t="n"/>
-      <c r="Z23" s="44" t="n"/>
-      <c r="AA23" s="44" t="n"/>
-      <c r="AB23" s="44" t="n"/>
-      <c r="AC23" s="44" t="n"/>
-      <c r="AD23" s="44" t="n"/>
-      <c r="AE23" s="44" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="49" t="n"/>
+      <c r="K23" s="49" t="n"/>
+      <c r="L23" s="49" t="n"/>
+      <c r="M23" s="49" t="n"/>
+      <c r="N23" s="49" t="n"/>
+      <c r="O23" s="49" t="n"/>
+      <c r="P23" s="49" t="n"/>
+      <c r="Q23" s="49" t="n"/>
+      <c r="R23" s="49" t="n"/>
+      <c r="S23" s="49" t="n"/>
+      <c r="T23" s="49" t="n"/>
+      <c r="U23" s="49" t="n"/>
+      <c r="V23" s="49" t="n"/>
+      <c r="W23" s="49" t="n"/>
+      <c r="X23" s="49" t="n"/>
+      <c r="Y23" s="49" t="n"/>
+      <c r="Z23" s="49" t="n"/>
+      <c r="AA23" s="49" t="n"/>
+      <c r="AB23" s="49" t="n"/>
+      <c r="AC23" s="49" t="n"/>
+      <c r="AD23" s="49" t="n"/>
+      <c r="AE23" s="49" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="39">
@@ -6707,32 +9545,32 @@
         <f>IF(프로젝트!$C24="","",프로젝트!$I24)</f>
         <v/>
       </c>
-      <c r="F24" s="44" t="n"/>
-      <c r="G24" s="44" t="n"/>
-      <c r="H24" s="44" t="n"/>
-      <c r="I24" s="44" t="n"/>
-      <c r="J24" s="44" t="n"/>
-      <c r="K24" s="44" t="n"/>
-      <c r="L24" s="44" t="n"/>
-      <c r="M24" s="44" t="n"/>
-      <c r="N24" s="44" t="n"/>
-      <c r="O24" s="44" t="n"/>
-      <c r="P24" s="44" t="n"/>
-      <c r="Q24" s="44" t="n"/>
-      <c r="R24" s="44" t="n"/>
-      <c r="S24" s="44" t="n"/>
-      <c r="T24" s="44" t="n"/>
-      <c r="U24" s="44" t="n"/>
-      <c r="V24" s="44" t="n"/>
-      <c r="W24" s="44" t="n"/>
-      <c r="X24" s="44" t="n"/>
-      <c r="Y24" s="44" t="n"/>
-      <c r="Z24" s="44" t="n"/>
-      <c r="AA24" s="44" t="n"/>
-      <c r="AB24" s="44" t="n"/>
-      <c r="AC24" s="44" t="n"/>
-      <c r="AD24" s="44" t="n"/>
-      <c r="AE24" s="44" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="49" t="n"/>
+      <c r="J24" s="49" t="n"/>
+      <c r="K24" s="49" t="n"/>
+      <c r="L24" s="49" t="n"/>
+      <c r="M24" s="49" t="n"/>
+      <c r="N24" s="49" t="n"/>
+      <c r="O24" s="49" t="n"/>
+      <c r="P24" s="49" t="n"/>
+      <c r="Q24" s="49" t="n"/>
+      <c r="R24" s="49" t="n"/>
+      <c r="S24" s="49" t="n"/>
+      <c r="T24" s="49" t="n"/>
+      <c r="U24" s="49" t="n"/>
+      <c r="V24" s="49" t="n"/>
+      <c r="W24" s="49" t="n"/>
+      <c r="X24" s="49" t="n"/>
+      <c r="Y24" s="49" t="n"/>
+      <c r="Z24" s="49" t="n"/>
+      <c r="AA24" s="49" t="n"/>
+      <c r="AB24" s="49" t="n"/>
+      <c r="AC24" s="49" t="n"/>
+      <c r="AD24" s="49" t="n"/>
+      <c r="AE24" s="49" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="39">
@@ -6751,32 +9589,32 @@
         <f>IF(프로젝트!$C25="","",프로젝트!$I25)</f>
         <v/>
       </c>
-      <c r="F25" s="44" t="n"/>
-      <c r="G25" s="44" t="n"/>
-      <c r="H25" s="44" t="n"/>
-      <c r="I25" s="44" t="n"/>
-      <c r="J25" s="44" t="n"/>
-      <c r="K25" s="44" t="n"/>
-      <c r="L25" s="44" t="n"/>
-      <c r="M25" s="44" t="n"/>
-      <c r="N25" s="44" t="n"/>
-      <c r="O25" s="44" t="n"/>
-      <c r="P25" s="44" t="n"/>
-      <c r="Q25" s="44" t="n"/>
-      <c r="R25" s="44" t="n"/>
-      <c r="S25" s="44" t="n"/>
-      <c r="T25" s="44" t="n"/>
-      <c r="U25" s="44" t="n"/>
-      <c r="V25" s="44" t="n"/>
-      <c r="W25" s="44" t="n"/>
-      <c r="X25" s="44" t="n"/>
-      <c r="Y25" s="44" t="n"/>
-      <c r="Z25" s="44" t="n"/>
-      <c r="AA25" s="44" t="n"/>
-      <c r="AB25" s="44" t="n"/>
-      <c r="AC25" s="44" t="n"/>
-      <c r="AD25" s="44" t="n"/>
-      <c r="AE25" s="44" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="49" t="n"/>
+      <c r="J25" s="49" t="n"/>
+      <c r="K25" s="49" t="n"/>
+      <c r="L25" s="49" t="n"/>
+      <c r="M25" s="49" t="n"/>
+      <c r="N25" s="49" t="n"/>
+      <c r="O25" s="49" t="n"/>
+      <c r="P25" s="49" t="n"/>
+      <c r="Q25" s="49" t="n"/>
+      <c r="R25" s="49" t="n"/>
+      <c r="S25" s="49" t="n"/>
+      <c r="T25" s="49" t="n"/>
+      <c r="U25" s="49" t="n"/>
+      <c r="V25" s="49" t="n"/>
+      <c r="W25" s="49" t="n"/>
+      <c r="X25" s="49" t="n"/>
+      <c r="Y25" s="49" t="n"/>
+      <c r="Z25" s="49" t="n"/>
+      <c r="AA25" s="49" t="n"/>
+      <c r="AB25" s="49" t="n"/>
+      <c r="AC25" s="49" t="n"/>
+      <c r="AD25" s="49" t="n"/>
+      <c r="AE25" s="49" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="39">
@@ -6795,32 +9633,32 @@
         <f>IF(프로젝트!$C26="","",프로젝트!$I26)</f>
         <v/>
       </c>
-      <c r="F26" s="44" t="n"/>
-      <c r="G26" s="44" t="n"/>
-      <c r="H26" s="44" t="n"/>
-      <c r="I26" s="44" t="n"/>
-      <c r="J26" s="44" t="n"/>
-      <c r="K26" s="44" t="n"/>
-      <c r="L26" s="44" t="n"/>
-      <c r="M26" s="44" t="n"/>
-      <c r="N26" s="44" t="n"/>
-      <c r="O26" s="44" t="n"/>
-      <c r="P26" s="44" t="n"/>
-      <c r="Q26" s="44" t="n"/>
-      <c r="R26" s="44" t="n"/>
-      <c r="S26" s="44" t="n"/>
-      <c r="T26" s="44" t="n"/>
-      <c r="U26" s="44" t="n"/>
-      <c r="V26" s="44" t="n"/>
-      <c r="W26" s="44" t="n"/>
-      <c r="X26" s="44" t="n"/>
-      <c r="Y26" s="44" t="n"/>
-      <c r="Z26" s="44" t="n"/>
-      <c r="AA26" s="44" t="n"/>
-      <c r="AB26" s="44" t="n"/>
-      <c r="AC26" s="44" t="n"/>
-      <c r="AD26" s="44" t="n"/>
-      <c r="AE26" s="44" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="49" t="n"/>
+      <c r="K26" s="49" t="n"/>
+      <c r="L26" s="49" t="n"/>
+      <c r="M26" s="49" t="n"/>
+      <c r="N26" s="49" t="n"/>
+      <c r="O26" s="49" t="n"/>
+      <c r="P26" s="49" t="n"/>
+      <c r="Q26" s="49" t="n"/>
+      <c r="R26" s="49" t="n"/>
+      <c r="S26" s="49" t="n"/>
+      <c r="T26" s="49" t="n"/>
+      <c r="U26" s="49" t="n"/>
+      <c r="V26" s="49" t="n"/>
+      <c r="W26" s="49" t="n"/>
+      <c r="X26" s="49" t="n"/>
+      <c r="Y26" s="49" t="n"/>
+      <c r="Z26" s="49" t="n"/>
+      <c r="AA26" s="49" t="n"/>
+      <c r="AB26" s="49" t="n"/>
+      <c r="AC26" s="49" t="n"/>
+      <c r="AD26" s="49" t="n"/>
+      <c r="AE26" s="49" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="39">
@@ -6839,32 +9677,32 @@
         <f>IF(프로젝트!$C27="","",프로젝트!$I27)</f>
         <v/>
       </c>
-      <c r="F27" s="44" t="n"/>
-      <c r="G27" s="44" t="n"/>
-      <c r="H27" s="44" t="n"/>
-      <c r="I27" s="44" t="n"/>
-      <c r="J27" s="44" t="n"/>
-      <c r="K27" s="44" t="n"/>
-      <c r="L27" s="44" t="n"/>
-      <c r="M27" s="44" t="n"/>
-      <c r="N27" s="44" t="n"/>
-      <c r="O27" s="44" t="n"/>
-      <c r="P27" s="44" t="n"/>
-      <c r="Q27" s="44" t="n"/>
-      <c r="R27" s="44" t="n"/>
-      <c r="S27" s="44" t="n"/>
-      <c r="T27" s="44" t="n"/>
-      <c r="U27" s="44" t="n"/>
-      <c r="V27" s="44" t="n"/>
-      <c r="W27" s="44" t="n"/>
-      <c r="X27" s="44" t="n"/>
-      <c r="Y27" s="44" t="n"/>
-      <c r="Z27" s="44" t="n"/>
-      <c r="AA27" s="44" t="n"/>
-      <c r="AB27" s="44" t="n"/>
-      <c r="AC27" s="44" t="n"/>
-      <c r="AD27" s="44" t="n"/>
-      <c r="AE27" s="44" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="49" t="n"/>
+      <c r="K27" s="49" t="n"/>
+      <c r="L27" s="49" t="n"/>
+      <c r="M27" s="49" t="n"/>
+      <c r="N27" s="49" t="n"/>
+      <c r="O27" s="49" t="n"/>
+      <c r="P27" s="49" t="n"/>
+      <c r="Q27" s="49" t="n"/>
+      <c r="R27" s="49" t="n"/>
+      <c r="S27" s="49" t="n"/>
+      <c r="T27" s="49" t="n"/>
+      <c r="U27" s="49" t="n"/>
+      <c r="V27" s="49" t="n"/>
+      <c r="W27" s="49" t="n"/>
+      <c r="X27" s="49" t="n"/>
+      <c r="Y27" s="49" t="n"/>
+      <c r="Z27" s="49" t="n"/>
+      <c r="AA27" s="49" t="n"/>
+      <c r="AB27" s="49" t="n"/>
+      <c r="AC27" s="49" t="n"/>
+      <c r="AD27" s="49" t="n"/>
+      <c r="AE27" s="49" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="39">
@@ -6883,32 +9721,32 @@
         <f>IF(프로젝트!$C28="","",프로젝트!$I28)</f>
         <v/>
       </c>
-      <c r="F28" s="44" t="n"/>
-      <c r="G28" s="44" t="n"/>
-      <c r="H28" s="44" t="n"/>
-      <c r="I28" s="44" t="n"/>
-      <c r="J28" s="44" t="n"/>
-      <c r="K28" s="44" t="n"/>
-      <c r="L28" s="44" t="n"/>
-      <c r="M28" s="44" t="n"/>
-      <c r="N28" s="44" t="n"/>
-      <c r="O28" s="44" t="n"/>
-      <c r="P28" s="44" t="n"/>
-      <c r="Q28" s="44" t="n"/>
-      <c r="R28" s="44" t="n"/>
-      <c r="S28" s="44" t="n"/>
-      <c r="T28" s="44" t="n"/>
-      <c r="U28" s="44" t="n"/>
-      <c r="V28" s="44" t="n"/>
-      <c r="W28" s="44" t="n"/>
-      <c r="X28" s="44" t="n"/>
-      <c r="Y28" s="44" t="n"/>
-      <c r="Z28" s="44" t="n"/>
-      <c r="AA28" s="44" t="n"/>
-      <c r="AB28" s="44" t="n"/>
-      <c r="AC28" s="44" t="n"/>
-      <c r="AD28" s="44" t="n"/>
-      <c r="AE28" s="44" t="n"/>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="49" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="49" t="n"/>
+      <c r="J28" s="49" t="n"/>
+      <c r="K28" s="49" t="n"/>
+      <c r="L28" s="49" t="n"/>
+      <c r="M28" s="49" t="n"/>
+      <c r="N28" s="49" t="n"/>
+      <c r="O28" s="49" t="n"/>
+      <c r="P28" s="49" t="n"/>
+      <c r="Q28" s="49" t="n"/>
+      <c r="R28" s="49" t="n"/>
+      <c r="S28" s="49" t="n"/>
+      <c r="T28" s="49" t="n"/>
+      <c r="U28" s="49" t="n"/>
+      <c r="V28" s="49" t="n"/>
+      <c r="W28" s="49" t="n"/>
+      <c r="X28" s="49" t="n"/>
+      <c r="Y28" s="49" t="n"/>
+      <c r="Z28" s="49" t="n"/>
+      <c r="AA28" s="49" t="n"/>
+      <c r="AB28" s="49" t="n"/>
+      <c r="AC28" s="49" t="n"/>
+      <c r="AD28" s="49" t="n"/>
+      <c r="AE28" s="49" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="39">
@@ -6927,32 +9765,32 @@
         <f>IF(프로젝트!$C29="","",프로젝트!$I29)</f>
         <v/>
       </c>
-      <c r="F29" s="44" t="n"/>
-      <c r="G29" s="44" t="n"/>
-      <c r="H29" s="44" t="n"/>
-      <c r="I29" s="44" t="n"/>
-      <c r="J29" s="44" t="n"/>
-      <c r="K29" s="44" t="n"/>
-      <c r="L29" s="44" t="n"/>
-      <c r="M29" s="44" t="n"/>
-      <c r="N29" s="44" t="n"/>
-      <c r="O29" s="44" t="n"/>
-      <c r="P29" s="44" t="n"/>
-      <c r="Q29" s="44" t="n"/>
-      <c r="R29" s="44" t="n"/>
-      <c r="S29" s="44" t="n"/>
-      <c r="T29" s="44" t="n"/>
-      <c r="U29" s="44" t="n"/>
-      <c r="V29" s="44" t="n"/>
-      <c r="W29" s="44" t="n"/>
-      <c r="X29" s="44" t="n"/>
-      <c r="Y29" s="44" t="n"/>
-      <c r="Z29" s="44" t="n"/>
-      <c r="AA29" s="44" t="n"/>
-      <c r="AB29" s="44" t="n"/>
-      <c r="AC29" s="44" t="n"/>
-      <c r="AD29" s="44" t="n"/>
-      <c r="AE29" s="44" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="49" t="n"/>
+      <c r="J29" s="49" t="n"/>
+      <c r="K29" s="49" t="n"/>
+      <c r="L29" s="49" t="n"/>
+      <c r="M29" s="49" t="n"/>
+      <c r="N29" s="49" t="n"/>
+      <c r="O29" s="49" t="n"/>
+      <c r="P29" s="49" t="n"/>
+      <c r="Q29" s="49" t="n"/>
+      <c r="R29" s="49" t="n"/>
+      <c r="S29" s="49" t="n"/>
+      <c r="T29" s="49" t="n"/>
+      <c r="U29" s="49" t="n"/>
+      <c r="V29" s="49" t="n"/>
+      <c r="W29" s="49" t="n"/>
+      <c r="X29" s="49" t="n"/>
+      <c r="Y29" s="49" t="n"/>
+      <c r="Z29" s="49" t="n"/>
+      <c r="AA29" s="49" t="n"/>
+      <c r="AB29" s="49" t="n"/>
+      <c r="AC29" s="49" t="n"/>
+      <c r="AD29" s="49" t="n"/>
+      <c r="AE29" s="49" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="39">
@@ -6971,32 +9809,32 @@
         <f>IF(프로젝트!$C30="","",프로젝트!$I30)</f>
         <v/>
       </c>
-      <c r="F30" s="44" t="n"/>
-      <c r="G30" s="44" t="n"/>
-      <c r="H30" s="44" t="n"/>
-      <c r="I30" s="44" t="n"/>
-      <c r="J30" s="44" t="n"/>
-      <c r="K30" s="44" t="n"/>
-      <c r="L30" s="44" t="n"/>
-      <c r="M30" s="44" t="n"/>
-      <c r="N30" s="44" t="n"/>
-      <c r="O30" s="44" t="n"/>
-      <c r="P30" s="44" t="n"/>
-      <c r="Q30" s="44" t="n"/>
-      <c r="R30" s="44" t="n"/>
-      <c r="S30" s="44" t="n"/>
-      <c r="T30" s="44" t="n"/>
-      <c r="U30" s="44" t="n"/>
-      <c r="V30" s="44" t="n"/>
-      <c r="W30" s="44" t="n"/>
-      <c r="X30" s="44" t="n"/>
-      <c r="Y30" s="44" t="n"/>
-      <c r="Z30" s="44" t="n"/>
-      <c r="AA30" s="44" t="n"/>
-      <c r="AB30" s="44" t="n"/>
-      <c r="AC30" s="44" t="n"/>
-      <c r="AD30" s="44" t="n"/>
-      <c r="AE30" s="44" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
+      <c r="J30" s="49" t="n"/>
+      <c r="K30" s="49" t="n"/>
+      <c r="L30" s="49" t="n"/>
+      <c r="M30" s="49" t="n"/>
+      <c r="N30" s="49" t="n"/>
+      <c r="O30" s="49" t="n"/>
+      <c r="P30" s="49" t="n"/>
+      <c r="Q30" s="49" t="n"/>
+      <c r="R30" s="49" t="n"/>
+      <c r="S30" s="49" t="n"/>
+      <c r="T30" s="49" t="n"/>
+      <c r="U30" s="49" t="n"/>
+      <c r="V30" s="49" t="n"/>
+      <c r="W30" s="49" t="n"/>
+      <c r="X30" s="49" t="n"/>
+      <c r="Y30" s="49" t="n"/>
+      <c r="Z30" s="49" t="n"/>
+      <c r="AA30" s="49" t="n"/>
+      <c r="AB30" s="49" t="n"/>
+      <c r="AC30" s="49" t="n"/>
+      <c r="AD30" s="49" t="n"/>
+      <c r="AE30" s="49" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="39">
@@ -7015,32 +9853,32 @@
         <f>IF(프로젝트!$C31="","",프로젝트!$I31)</f>
         <v/>
       </c>
-      <c r="F31" s="44" t="n"/>
-      <c r="G31" s="44" t="n"/>
-      <c r="H31" s="44" t="n"/>
-      <c r="I31" s="44" t="n"/>
-      <c r="J31" s="44" t="n"/>
-      <c r="K31" s="44" t="n"/>
-      <c r="L31" s="44" t="n"/>
-      <c r="M31" s="44" t="n"/>
-      <c r="N31" s="44" t="n"/>
-      <c r="O31" s="44" t="n"/>
-      <c r="P31" s="44" t="n"/>
-      <c r="Q31" s="44" t="n"/>
-      <c r="R31" s="44" t="n"/>
-      <c r="S31" s="44" t="n"/>
-      <c r="T31" s="44" t="n"/>
-      <c r="U31" s="44" t="n"/>
-      <c r="V31" s="44" t="n"/>
-      <c r="W31" s="44" t="n"/>
-      <c r="X31" s="44" t="n"/>
-      <c r="Y31" s="44" t="n"/>
-      <c r="Z31" s="44" t="n"/>
-      <c r="AA31" s="44" t="n"/>
-      <c r="AB31" s="44" t="n"/>
-      <c r="AC31" s="44" t="n"/>
-      <c r="AD31" s="44" t="n"/>
-      <c r="AE31" s="44" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="49" t="n"/>
+      <c r="J31" s="49" t="n"/>
+      <c r="K31" s="49" t="n"/>
+      <c r="L31" s="49" t="n"/>
+      <c r="M31" s="49" t="n"/>
+      <c r="N31" s="49" t="n"/>
+      <c r="O31" s="49" t="n"/>
+      <c r="P31" s="49" t="n"/>
+      <c r="Q31" s="49" t="n"/>
+      <c r="R31" s="49" t="n"/>
+      <c r="S31" s="49" t="n"/>
+      <c r="T31" s="49" t="n"/>
+      <c r="U31" s="49" t="n"/>
+      <c r="V31" s="49" t="n"/>
+      <c r="W31" s="49" t="n"/>
+      <c r="X31" s="49" t="n"/>
+      <c r="Y31" s="49" t="n"/>
+      <c r="Z31" s="49" t="n"/>
+      <c r="AA31" s="49" t="n"/>
+      <c r="AB31" s="49" t="n"/>
+      <c r="AC31" s="49" t="n"/>
+      <c r="AD31" s="49" t="n"/>
+      <c r="AE31" s="49" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="39">
@@ -7059,32 +9897,32 @@
         <f>IF(프로젝트!$C32="","",프로젝트!$I32)</f>
         <v/>
       </c>
-      <c r="F32" s="44" t="n"/>
-      <c r="G32" s="44" t="n"/>
-      <c r="H32" s="44" t="n"/>
-      <c r="I32" s="44" t="n"/>
-      <c r="J32" s="44" t="n"/>
-      <c r="K32" s="44" t="n"/>
-      <c r="L32" s="44" t="n"/>
-      <c r="M32" s="44" t="n"/>
-      <c r="N32" s="44" t="n"/>
-      <c r="O32" s="44" t="n"/>
-      <c r="P32" s="44" t="n"/>
-      <c r="Q32" s="44" t="n"/>
-      <c r="R32" s="44" t="n"/>
-      <c r="S32" s="44" t="n"/>
-      <c r="T32" s="44" t="n"/>
-      <c r="U32" s="44" t="n"/>
-      <c r="V32" s="44" t="n"/>
-      <c r="W32" s="44" t="n"/>
-      <c r="X32" s="44" t="n"/>
-      <c r="Y32" s="44" t="n"/>
-      <c r="Z32" s="44" t="n"/>
-      <c r="AA32" s="44" t="n"/>
-      <c r="AB32" s="44" t="n"/>
-      <c r="AC32" s="44" t="n"/>
-      <c r="AD32" s="44" t="n"/>
-      <c r="AE32" s="44" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="49" t="n"/>
+      <c r="J32" s="49" t="n"/>
+      <c r="K32" s="49" t="n"/>
+      <c r="L32" s="49" t="n"/>
+      <c r="M32" s="49" t="n"/>
+      <c r="N32" s="49" t="n"/>
+      <c r="O32" s="49" t="n"/>
+      <c r="P32" s="49" t="n"/>
+      <c r="Q32" s="49" t="n"/>
+      <c r="R32" s="49" t="n"/>
+      <c r="S32" s="49" t="n"/>
+      <c r="T32" s="49" t="n"/>
+      <c r="U32" s="49" t="n"/>
+      <c r="V32" s="49" t="n"/>
+      <c r="W32" s="49" t="n"/>
+      <c r="X32" s="49" t="n"/>
+      <c r="Y32" s="49" t="n"/>
+      <c r="Z32" s="49" t="n"/>
+      <c r="AA32" s="49" t="n"/>
+      <c r="AB32" s="49" t="n"/>
+      <c r="AC32" s="49" t="n"/>
+      <c r="AD32" s="49" t="n"/>
+      <c r="AE32" s="49" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="39">
@@ -7103,32 +9941,32 @@
         <f>IF(프로젝트!$C33="","",프로젝트!$I33)</f>
         <v/>
       </c>
-      <c r="F33" s="44" t="n"/>
-      <c r="G33" s="44" t="n"/>
-      <c r="H33" s="44" t="n"/>
-      <c r="I33" s="44" t="n"/>
-      <c r="J33" s="44" t="n"/>
-      <c r="K33" s="44" t="n"/>
-      <c r="L33" s="44" t="n"/>
-      <c r="M33" s="44" t="n"/>
-      <c r="N33" s="44" t="n"/>
-      <c r="O33" s="44" t="n"/>
-      <c r="P33" s="44" t="n"/>
-      <c r="Q33" s="44" t="n"/>
-      <c r="R33" s="44" t="n"/>
-      <c r="S33" s="44" t="n"/>
-      <c r="T33" s="44" t="n"/>
-      <c r="U33" s="44" t="n"/>
-      <c r="V33" s="44" t="n"/>
-      <c r="W33" s="44" t="n"/>
-      <c r="X33" s="44" t="n"/>
-      <c r="Y33" s="44" t="n"/>
-      <c r="Z33" s="44" t="n"/>
-      <c r="AA33" s="44" t="n"/>
-      <c r="AB33" s="44" t="n"/>
-      <c r="AC33" s="44" t="n"/>
-      <c r="AD33" s="44" t="n"/>
-      <c r="AE33" s="44" t="n"/>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="49" t="n"/>
+      <c r="J33" s="49" t="n"/>
+      <c r="K33" s="49" t="n"/>
+      <c r="L33" s="49" t="n"/>
+      <c r="M33" s="49" t="n"/>
+      <c r="N33" s="49" t="n"/>
+      <c r="O33" s="49" t="n"/>
+      <c r="P33" s="49" t="n"/>
+      <c r="Q33" s="49" t="n"/>
+      <c r="R33" s="49" t="n"/>
+      <c r="S33" s="49" t="n"/>
+      <c r="T33" s="49" t="n"/>
+      <c r="U33" s="49" t="n"/>
+      <c r="V33" s="49" t="n"/>
+      <c r="W33" s="49" t="n"/>
+      <c r="X33" s="49" t="n"/>
+      <c r="Y33" s="49" t="n"/>
+      <c r="Z33" s="49" t="n"/>
+      <c r="AA33" s="49" t="n"/>
+      <c r="AB33" s="49" t="n"/>
+      <c r="AC33" s="49" t="n"/>
+      <c r="AD33" s="49" t="n"/>
+      <c r="AE33" s="49" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="39">
@@ -7147,32 +9985,32 @@
         <f>IF(프로젝트!$C34="","",프로젝트!$I34)</f>
         <v/>
       </c>
-      <c r="F34" s="44" t="n"/>
-      <c r="G34" s="44" t="n"/>
-      <c r="H34" s="44" t="n"/>
-      <c r="I34" s="44" t="n"/>
-      <c r="J34" s="44" t="n"/>
-      <c r="K34" s="44" t="n"/>
-      <c r="L34" s="44" t="n"/>
-      <c r="M34" s="44" t="n"/>
-      <c r="N34" s="44" t="n"/>
-      <c r="O34" s="44" t="n"/>
-      <c r="P34" s="44" t="n"/>
-      <c r="Q34" s="44" t="n"/>
-      <c r="R34" s="44" t="n"/>
-      <c r="S34" s="44" t="n"/>
-      <c r="T34" s="44" t="n"/>
-      <c r="U34" s="44" t="n"/>
-      <c r="V34" s="44" t="n"/>
-      <c r="W34" s="44" t="n"/>
-      <c r="X34" s="44" t="n"/>
-      <c r="Y34" s="44" t="n"/>
-      <c r="Z34" s="44" t="n"/>
-      <c r="AA34" s="44" t="n"/>
-      <c r="AB34" s="44" t="n"/>
-      <c r="AC34" s="44" t="n"/>
-      <c r="AD34" s="44" t="n"/>
-      <c r="AE34" s="44" t="n"/>
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="49" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="49" t="n"/>
+      <c r="J34" s="49" t="n"/>
+      <c r="K34" s="49" t="n"/>
+      <c r="L34" s="49" t="n"/>
+      <c r="M34" s="49" t="n"/>
+      <c r="N34" s="49" t="n"/>
+      <c r="O34" s="49" t="n"/>
+      <c r="P34" s="49" t="n"/>
+      <c r="Q34" s="49" t="n"/>
+      <c r="R34" s="49" t="n"/>
+      <c r="S34" s="49" t="n"/>
+      <c r="T34" s="49" t="n"/>
+      <c r="U34" s="49" t="n"/>
+      <c r="V34" s="49" t="n"/>
+      <c r="W34" s="49" t="n"/>
+      <c r="X34" s="49" t="n"/>
+      <c r="Y34" s="49" t="n"/>
+      <c r="Z34" s="49" t="n"/>
+      <c r="AA34" s="49" t="n"/>
+      <c r="AB34" s="49" t="n"/>
+      <c r="AC34" s="49" t="n"/>
+      <c r="AD34" s="49" t="n"/>
+      <c r="AE34" s="49" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="39">
@@ -7191,32 +10029,32 @@
         <f>IF(프로젝트!$C35="","",프로젝트!$I35)</f>
         <v/>
       </c>
-      <c r="F35" s="44" t="n"/>
-      <c r="G35" s="44" t="n"/>
-      <c r="H35" s="44" t="n"/>
-      <c r="I35" s="44" t="n"/>
-      <c r="J35" s="44" t="n"/>
-      <c r="K35" s="44" t="n"/>
-      <c r="L35" s="44" t="n"/>
-      <c r="M35" s="44" t="n"/>
-      <c r="N35" s="44" t="n"/>
-      <c r="O35" s="44" t="n"/>
-      <c r="P35" s="44" t="n"/>
-      <c r="Q35" s="44" t="n"/>
-      <c r="R35" s="44" t="n"/>
-      <c r="S35" s="44" t="n"/>
-      <c r="T35" s="44" t="n"/>
-      <c r="U35" s="44" t="n"/>
-      <c r="V35" s="44" t="n"/>
-      <c r="W35" s="44" t="n"/>
-      <c r="X35" s="44" t="n"/>
-      <c r="Y35" s="44" t="n"/>
-      <c r="Z35" s="44" t="n"/>
-      <c r="AA35" s="44" t="n"/>
-      <c r="AB35" s="44" t="n"/>
-      <c r="AC35" s="44" t="n"/>
-      <c r="AD35" s="44" t="n"/>
-      <c r="AE35" s="44" t="n"/>
+      <c r="F35" s="49" t="n"/>
+      <c r="G35" s="49" t="n"/>
+      <c r="H35" s="49" t="n"/>
+      <c r="I35" s="49" t="n"/>
+      <c r="J35" s="49" t="n"/>
+      <c r="K35" s="49" t="n"/>
+      <c r="L35" s="49" t="n"/>
+      <c r="M35" s="49" t="n"/>
+      <c r="N35" s="49" t="n"/>
+      <c r="O35" s="49" t="n"/>
+      <c r="P35" s="49" t="n"/>
+      <c r="Q35" s="49" t="n"/>
+      <c r="R35" s="49" t="n"/>
+      <c r="S35" s="49" t="n"/>
+      <c r="T35" s="49" t="n"/>
+      <c r="U35" s="49" t="n"/>
+      <c r="V35" s="49" t="n"/>
+      <c r="W35" s="49" t="n"/>
+      <c r="X35" s="49" t="n"/>
+      <c r="Y35" s="49" t="n"/>
+      <c r="Z35" s="49" t="n"/>
+      <c r="AA35" s="49" t="n"/>
+      <c r="AB35" s="49" t="n"/>
+      <c r="AC35" s="49" t="n"/>
+      <c r="AD35" s="49" t="n"/>
+      <c r="AE35" s="49" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F6:AE35">
@@ -7252,4 +10090,198 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>⚙️ 설정 - 드롭다운 목록 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>아래 목록을 수정하면 각 시트의 드롭다운 선택지가 바뀝니다. (항목 추가 시 이름 관리자에서 범위 확장 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>팀원</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>상태별 색상</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>이영희</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>마케팅</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>박민수</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>정수진</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>지연</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>최지훈</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>지연</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/프로젝트_트랙커.xlsx
+++ b/프로젝트_트랙커.xlsx
@@ -3618,7 +3618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L105"/>
+  <dimension ref="B2:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3633,6 +3633,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -3751,6 +3752,10 @@
         <v/>
       </c>
       <c r="L6" s="39" t="inlineStr"/>
+      <c r="N6">
+        <f>IF($B6="","",$C6&amp;"|"&amp;COUNTIF($C$6:$C6,$C6))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="24" t="inlineStr">
@@ -3797,6 +3802,10 @@
         <v/>
       </c>
       <c r="L7" s="39" t="inlineStr"/>
+      <c r="N7">
+        <f>IF($B7="","",$C7&amp;"|"&amp;COUNTIF($C$6:$C7,$C7))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="24" t="inlineStr">
@@ -3843,6 +3852,10 @@
         <v/>
       </c>
       <c r="L8" s="39" t="inlineStr"/>
+      <c r="N8">
+        <f>IF($B8="","",$C8&amp;"|"&amp;COUNTIF($C$6:$C8,$C8))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="24" t="inlineStr">
@@ -3889,6 +3902,10 @@
         <v/>
       </c>
       <c r="L9" s="39" t="inlineStr"/>
+      <c r="N9">
+        <f>IF($B9="","",$C9&amp;"|"&amp;COUNTIF($C$6:$C9,$C9))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="24" t="inlineStr">
@@ -3939,6 +3956,10 @@
           <t>심사 기간 고려</t>
         </is>
       </c>
+      <c r="N10">
+        <f>IF($B10="","",$C10&amp;"|"&amp;COUNTIF($C$6:$C10,$C10))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="24" t="inlineStr">
@@ -3988,6 +4009,10 @@
         <is>
           <t>외주사 회신 대기</t>
         </is>
+      </c>
+      <c r="N11">
+        <f>IF($B11="","",$C11&amp;"|"&amp;COUNTIF($C$6:$C11,$C11))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -4005,6 +4030,10 @@
         <v/>
       </c>
       <c r="L12" s="39" t="n"/>
+      <c r="N12">
+        <f>IF($B12="","",$C12&amp;"|"&amp;COUNTIF($C$6:$C12,$C12))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="24" t="n"/>
@@ -4021,6 +4050,10 @@
         <v/>
       </c>
       <c r="L13" s="39" t="n"/>
+      <c r="N13">
+        <f>IF($B13="","",$C13&amp;"|"&amp;COUNTIF($C$6:$C13,$C13))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="24" t="n"/>
@@ -4037,6 +4070,10 @@
         <v/>
       </c>
       <c r="L14" s="39" t="n"/>
+      <c r="N14">
+        <f>IF($B14="","",$C14&amp;"|"&amp;COUNTIF($C$6:$C14,$C14))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="24" t="n"/>
@@ -4053,6 +4090,10 @@
         <v/>
       </c>
       <c r="L15" s="39" t="n"/>
+      <c r="N15">
+        <f>IF($B15="","",$C15&amp;"|"&amp;COUNTIF($C$6:$C15,$C15))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="24" t="n"/>
@@ -4069,6 +4110,10 @@
         <v/>
       </c>
       <c r="L16" s="39" t="n"/>
+      <c r="N16">
+        <f>IF($B16="","",$C16&amp;"|"&amp;COUNTIF($C$6:$C16,$C16))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="24" t="n"/>
@@ -4085,6 +4130,10 @@
         <v/>
       </c>
       <c r="L17" s="39" t="n"/>
+      <c r="N17">
+        <f>IF($B17="","",$C17&amp;"|"&amp;COUNTIF($C$6:$C17,$C17))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="24" t="n"/>
@@ -4101,6 +4150,10 @@
         <v/>
       </c>
       <c r="L18" s="39" t="n"/>
+      <c r="N18">
+        <f>IF($B18="","",$C18&amp;"|"&amp;COUNTIF($C$6:$C18,$C18))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="24" t="n"/>
@@ -4117,6 +4170,10 @@
         <v/>
       </c>
       <c r="L19" s="39" t="n"/>
+      <c r="N19">
+        <f>IF($B19="","",$C19&amp;"|"&amp;COUNTIF($C$6:$C19,$C19))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="24" t="n"/>
@@ -4133,6 +4190,10 @@
         <v/>
       </c>
       <c r="L20" s="39" t="n"/>
+      <c r="N20">
+        <f>IF($B20="","",$C20&amp;"|"&amp;COUNTIF($C$6:$C20,$C20))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="24" t="n"/>
@@ -4149,6 +4210,10 @@
         <v/>
       </c>
       <c r="L21" s="39" t="n"/>
+      <c r="N21">
+        <f>IF($B21="","",$C21&amp;"|"&amp;COUNTIF($C$6:$C21,$C21))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="24" t="n"/>
@@ -4165,6 +4230,10 @@
         <v/>
       </c>
       <c r="L22" s="39" t="n"/>
+      <c r="N22">
+        <f>IF($B22="","",$C22&amp;"|"&amp;COUNTIF($C$6:$C22,$C22))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="24" t="n"/>
@@ -4181,6 +4250,10 @@
         <v/>
       </c>
       <c r="L23" s="39" t="n"/>
+      <c r="N23">
+        <f>IF($B23="","",$C23&amp;"|"&amp;COUNTIF($C$6:$C23,$C23))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="24" t="n"/>
@@ -4197,6 +4270,10 @@
         <v/>
       </c>
       <c r="L24" s="39" t="n"/>
+      <c r="N24">
+        <f>IF($B24="","",$C24&amp;"|"&amp;COUNTIF($C$6:$C24,$C24))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="24" t="n"/>
@@ -4213,6 +4290,10 @@
         <v/>
       </c>
       <c r="L25" s="39" t="n"/>
+      <c r="N25">
+        <f>IF($B25="","",$C25&amp;"|"&amp;COUNTIF($C$6:$C25,$C25))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="24" t="n"/>
@@ -4229,6 +4310,10 @@
         <v/>
       </c>
       <c r="L26" s="39" t="n"/>
+      <c r="N26">
+        <f>IF($B26="","",$C26&amp;"|"&amp;COUNTIF($C$6:$C26,$C26))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="24" t="n"/>
@@ -4245,6 +4330,10 @@
         <v/>
       </c>
       <c r="L27" s="39" t="n"/>
+      <c r="N27">
+        <f>IF($B27="","",$C27&amp;"|"&amp;COUNTIF($C$6:$C27,$C27))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="24" t="n"/>
@@ -4261,6 +4350,10 @@
         <v/>
       </c>
       <c r="L28" s="39" t="n"/>
+      <c r="N28">
+        <f>IF($B28="","",$C28&amp;"|"&amp;COUNTIF($C$6:$C28,$C28))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="24" t="n"/>
@@ -4277,6 +4370,10 @@
         <v/>
       </c>
       <c r="L29" s="39" t="n"/>
+      <c r="N29">
+        <f>IF($B29="","",$C29&amp;"|"&amp;COUNTIF($C$6:$C29,$C29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="24" t="n"/>
@@ -4293,6 +4390,10 @@
         <v/>
       </c>
       <c r="L30" s="39" t="n"/>
+      <c r="N30">
+        <f>IF($B30="","",$C30&amp;"|"&amp;COUNTIF($C$6:$C30,$C30))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="24" t="n"/>
@@ -4309,6 +4410,10 @@
         <v/>
       </c>
       <c r="L31" s="39" t="n"/>
+      <c r="N31">
+        <f>IF($B31="","",$C31&amp;"|"&amp;COUNTIF($C$6:$C31,$C31))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="24" t="n"/>
@@ -4325,6 +4430,10 @@
         <v/>
       </c>
       <c r="L32" s="39" t="n"/>
+      <c r="N32">
+        <f>IF($B32="","",$C32&amp;"|"&amp;COUNTIF($C$6:$C32,$C32))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="24" t="n"/>
@@ -4341,6 +4450,10 @@
         <v/>
       </c>
       <c r="L33" s="39" t="n"/>
+      <c r="N33">
+        <f>IF($B33="","",$C33&amp;"|"&amp;COUNTIF($C$6:$C33,$C33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="24" t="n"/>
@@ -4357,6 +4470,10 @@
         <v/>
       </c>
       <c r="L34" s="39" t="n"/>
+      <c r="N34">
+        <f>IF($B34="","",$C34&amp;"|"&amp;COUNTIF($C$6:$C34,$C34))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="24" t="n"/>
@@ -4373,6 +4490,10 @@
         <v/>
       </c>
       <c r="L35" s="39" t="n"/>
+      <c r="N35">
+        <f>IF($B35="","",$C35&amp;"|"&amp;COUNTIF($C$6:$C35,$C35))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="24" t="n"/>
@@ -4389,6 +4510,10 @@
         <v/>
       </c>
       <c r="L36" s="39" t="n"/>
+      <c r="N36">
+        <f>IF($B36="","",$C36&amp;"|"&amp;COUNTIF($C$6:$C36,$C36))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="24" t="n"/>
@@ -4405,6 +4530,10 @@
         <v/>
       </c>
       <c r="L37" s="39" t="n"/>
+      <c r="N37">
+        <f>IF($B37="","",$C37&amp;"|"&amp;COUNTIF($C$6:$C37,$C37))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="24" t="n"/>
@@ -4421,6 +4550,10 @@
         <v/>
       </c>
       <c r="L38" s="39" t="n"/>
+      <c r="N38">
+        <f>IF($B38="","",$C38&amp;"|"&amp;COUNTIF($C$6:$C38,$C38))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="24" t="n"/>
@@ -4437,6 +4570,10 @@
         <v/>
       </c>
       <c r="L39" s="39" t="n"/>
+      <c r="N39">
+        <f>IF($B39="","",$C39&amp;"|"&amp;COUNTIF($C$6:$C39,$C39))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="24" t="n"/>
@@ -4453,6 +4590,10 @@
         <v/>
       </c>
       <c r="L40" s="39" t="n"/>
+      <c r="N40">
+        <f>IF($B40="","",$C40&amp;"|"&amp;COUNTIF($C$6:$C40,$C40))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="24" t="n"/>
@@ -4469,6 +4610,10 @@
         <v/>
       </c>
       <c r="L41" s="39" t="n"/>
+      <c r="N41">
+        <f>IF($B41="","",$C41&amp;"|"&amp;COUNTIF($C$6:$C41,$C41))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="24" t="n"/>
@@ -4485,6 +4630,10 @@
         <v/>
       </c>
       <c r="L42" s="39" t="n"/>
+      <c r="N42">
+        <f>IF($B42="","",$C42&amp;"|"&amp;COUNTIF($C$6:$C42,$C42))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="24" t="n"/>
@@ -4501,6 +4650,10 @@
         <v/>
       </c>
       <c r="L43" s="39" t="n"/>
+      <c r="N43">
+        <f>IF($B43="","",$C43&amp;"|"&amp;COUNTIF($C$6:$C43,$C43))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="24" t="n"/>
@@ -4517,6 +4670,10 @@
         <v/>
       </c>
       <c r="L44" s="39" t="n"/>
+      <c r="N44">
+        <f>IF($B44="","",$C44&amp;"|"&amp;COUNTIF($C$6:$C44,$C44))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="24" t="n"/>
@@ -4533,6 +4690,10 @@
         <v/>
       </c>
       <c r="L45" s="39" t="n"/>
+      <c r="N45">
+        <f>IF($B45="","",$C45&amp;"|"&amp;COUNTIF($C$6:$C45,$C45))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="24" t="n"/>
@@ -4549,6 +4710,10 @@
         <v/>
       </c>
       <c r="L46" s="39" t="n"/>
+      <c r="N46">
+        <f>IF($B46="","",$C46&amp;"|"&amp;COUNTIF($C$6:$C46,$C46))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="24" t="n"/>
@@ -4565,6 +4730,10 @@
         <v/>
       </c>
       <c r="L47" s="39" t="n"/>
+      <c r="N47">
+        <f>IF($B47="","",$C47&amp;"|"&amp;COUNTIF($C$6:$C47,$C47))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="24" t="n"/>
@@ -4581,6 +4750,10 @@
         <v/>
       </c>
       <c r="L48" s="39" t="n"/>
+      <c r="N48">
+        <f>IF($B48="","",$C48&amp;"|"&amp;COUNTIF($C$6:$C48,$C48))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="24" t="n"/>
@@ -4597,6 +4770,10 @@
         <v/>
       </c>
       <c r="L49" s="39" t="n"/>
+      <c r="N49">
+        <f>IF($B49="","",$C49&amp;"|"&amp;COUNTIF($C$6:$C49,$C49))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="24" t="n"/>
@@ -4613,6 +4790,10 @@
         <v/>
       </c>
       <c r="L50" s="39" t="n"/>
+      <c r="N50">
+        <f>IF($B50="","",$C50&amp;"|"&amp;COUNTIF($C$6:$C50,$C50))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="24" t="n"/>
@@ -4629,6 +4810,10 @@
         <v/>
       </c>
       <c r="L51" s="39" t="n"/>
+      <c r="N51">
+        <f>IF($B51="","",$C51&amp;"|"&amp;COUNTIF($C$6:$C51,$C51))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="24" t="n"/>
@@ -4645,6 +4830,10 @@
         <v/>
       </c>
       <c r="L52" s="39" t="n"/>
+      <c r="N52">
+        <f>IF($B52="","",$C52&amp;"|"&amp;COUNTIF($C$6:$C52,$C52))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="B53" s="24" t="n"/>
@@ -4661,6 +4850,10 @@
         <v/>
       </c>
       <c r="L53" s="39" t="n"/>
+      <c r="N53">
+        <f>IF($B53="","",$C53&amp;"|"&amp;COUNTIF($C$6:$C53,$C53))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="24" t="n"/>
@@ -4677,6 +4870,10 @@
         <v/>
       </c>
       <c r="L54" s="39" t="n"/>
+      <c r="N54">
+        <f>IF($B54="","",$C54&amp;"|"&amp;COUNTIF($C$6:$C54,$C54))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="24" t="n"/>
@@ -4693,6 +4890,10 @@
         <v/>
       </c>
       <c r="L55" s="39" t="n"/>
+      <c r="N55">
+        <f>IF($B55="","",$C55&amp;"|"&amp;COUNTIF($C$6:$C55,$C55))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="24" t="n"/>
@@ -4709,6 +4910,10 @@
         <v/>
       </c>
       <c r="L56" s="39" t="n"/>
+      <c r="N56">
+        <f>IF($B56="","",$C56&amp;"|"&amp;COUNTIF($C$6:$C56,$C56))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="B57" s="24" t="n"/>
@@ -4725,6 +4930,10 @@
         <v/>
       </c>
       <c r="L57" s="39" t="n"/>
+      <c r="N57">
+        <f>IF($B57="","",$C57&amp;"|"&amp;COUNTIF($C$6:$C57,$C57))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="24" t="n"/>
@@ -4741,6 +4950,10 @@
         <v/>
       </c>
       <c r="L58" s="39" t="n"/>
+      <c r="N58">
+        <f>IF($B58="","",$C58&amp;"|"&amp;COUNTIF($C$6:$C58,$C58))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="B59" s="24" t="n"/>
@@ -4757,6 +4970,10 @@
         <v/>
       </c>
       <c r="L59" s="39" t="n"/>
+      <c r="N59">
+        <f>IF($B59="","",$C59&amp;"|"&amp;COUNTIF($C$6:$C59,$C59))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="24" t="n"/>
@@ -4773,6 +4990,10 @@
         <v/>
       </c>
       <c r="L60" s="39" t="n"/>
+      <c r="N60">
+        <f>IF($B60="","",$C60&amp;"|"&amp;COUNTIF($C$6:$C60,$C60))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="B61" s="24" t="n"/>
@@ -4789,6 +5010,10 @@
         <v/>
       </c>
       <c r="L61" s="39" t="n"/>
+      <c r="N61">
+        <f>IF($B61="","",$C61&amp;"|"&amp;COUNTIF($C$6:$C61,$C61))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="24" t="n"/>
@@ -4805,6 +5030,10 @@
         <v/>
       </c>
       <c r="L62" s="39" t="n"/>
+      <c r="N62">
+        <f>IF($B62="","",$C62&amp;"|"&amp;COUNTIF($C$6:$C62,$C62))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="24" t="n"/>
@@ -4821,6 +5050,10 @@
         <v/>
       </c>
       <c r="L63" s="39" t="n"/>
+      <c r="N63">
+        <f>IF($B63="","",$C63&amp;"|"&amp;COUNTIF($C$6:$C63,$C63))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="24" t="n"/>
@@ -4837,6 +5070,10 @@
         <v/>
       </c>
       <c r="L64" s="39" t="n"/>
+      <c r="N64">
+        <f>IF($B64="","",$C64&amp;"|"&amp;COUNTIF($C$6:$C64,$C64))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="24" t="n"/>
@@ -4853,6 +5090,10 @@
         <v/>
       </c>
       <c r="L65" s="39" t="n"/>
+      <c r="N65">
+        <f>IF($B65="","",$C65&amp;"|"&amp;COUNTIF($C$6:$C65,$C65))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="24" t="n"/>
@@ -4869,6 +5110,10 @@
         <v/>
       </c>
       <c r="L66" s="39" t="n"/>
+      <c r="N66">
+        <f>IF($B66="","",$C66&amp;"|"&amp;COUNTIF($C$6:$C66,$C66))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="24" t="n"/>
@@ -4885,6 +5130,10 @@
         <v/>
       </c>
       <c r="L67" s="39" t="n"/>
+      <c r="N67">
+        <f>IF($B67="","",$C67&amp;"|"&amp;COUNTIF($C$6:$C67,$C67))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="24" t="n"/>
@@ -4901,6 +5150,10 @@
         <v/>
       </c>
       <c r="L68" s="39" t="n"/>
+      <c r="N68">
+        <f>IF($B68="","",$C68&amp;"|"&amp;COUNTIF($C$6:$C68,$C68))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="24" t="n"/>
@@ -4917,6 +5170,10 @@
         <v/>
       </c>
       <c r="L69" s="39" t="n"/>
+      <c r="N69">
+        <f>IF($B69="","",$C69&amp;"|"&amp;COUNTIF($C$6:$C69,$C69))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="24" t="n"/>
@@ -4933,6 +5190,10 @@
         <v/>
       </c>
       <c r="L70" s="39" t="n"/>
+      <c r="N70">
+        <f>IF($B70="","",$C70&amp;"|"&amp;COUNTIF($C$6:$C70,$C70))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="24" t="n"/>
@@ -4949,6 +5210,10 @@
         <v/>
       </c>
       <c r="L71" s="39" t="n"/>
+      <c r="N71">
+        <f>IF($B71="","",$C71&amp;"|"&amp;COUNTIF($C$6:$C71,$C71))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="B72" s="24" t="n"/>
@@ -4965,6 +5230,10 @@
         <v/>
       </c>
       <c r="L72" s="39" t="n"/>
+      <c r="N72">
+        <f>IF($B72="","",$C72&amp;"|"&amp;COUNTIF($C$6:$C72,$C72))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="B73" s="24" t="n"/>
@@ -4981,6 +5250,10 @@
         <v/>
       </c>
       <c r="L73" s="39" t="n"/>
+      <c r="N73">
+        <f>IF($B73="","",$C73&amp;"|"&amp;COUNTIF($C$6:$C73,$C73))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="24" t="n"/>
@@ -4997,6 +5270,10 @@
         <v/>
       </c>
       <c r="L74" s="39" t="n"/>
+      <c r="N74">
+        <f>IF($B74="","",$C74&amp;"|"&amp;COUNTIF($C$6:$C74,$C74))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="24" t="n"/>
@@ -5013,6 +5290,10 @@
         <v/>
       </c>
       <c r="L75" s="39" t="n"/>
+      <c r="N75">
+        <f>IF($B75="","",$C75&amp;"|"&amp;COUNTIF($C$6:$C75,$C75))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="24" t="n"/>
@@ -5029,6 +5310,10 @@
         <v/>
       </c>
       <c r="L76" s="39" t="n"/>
+      <c r="N76">
+        <f>IF($B76="","",$C76&amp;"|"&amp;COUNTIF($C$6:$C76,$C76))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="24" t="n"/>
@@ -5045,6 +5330,10 @@
         <v/>
       </c>
       <c r="L77" s="39" t="n"/>
+      <c r="N77">
+        <f>IF($B77="","",$C77&amp;"|"&amp;COUNTIF($C$6:$C77,$C77))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="24" t="n"/>
@@ -5061,6 +5350,10 @@
         <v/>
       </c>
       <c r="L78" s="39" t="n"/>
+      <c r="N78">
+        <f>IF($B78="","",$C78&amp;"|"&amp;COUNTIF($C$6:$C78,$C78))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="24" t="n"/>
@@ -5077,6 +5370,10 @@
         <v/>
       </c>
       <c r="L79" s="39" t="n"/>
+      <c r="N79">
+        <f>IF($B79="","",$C79&amp;"|"&amp;COUNTIF($C$6:$C79,$C79))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="24" t="n"/>
@@ -5093,6 +5390,10 @@
         <v/>
       </c>
       <c r="L80" s="39" t="n"/>
+      <c r="N80">
+        <f>IF($B80="","",$C80&amp;"|"&amp;COUNTIF($C$6:$C80,$C80))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="24" t="n"/>
@@ -5109,6 +5410,10 @@
         <v/>
       </c>
       <c r="L81" s="39" t="n"/>
+      <c r="N81">
+        <f>IF($B81="","",$C81&amp;"|"&amp;COUNTIF($C$6:$C81,$C81))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="24" t="n"/>
@@ -5125,6 +5430,10 @@
         <v/>
       </c>
       <c r="L82" s="39" t="n"/>
+      <c r="N82">
+        <f>IF($B82="","",$C82&amp;"|"&amp;COUNTIF($C$6:$C82,$C82))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="24" t="n"/>
@@ -5141,6 +5450,10 @@
         <v/>
       </c>
       <c r="L83" s="39" t="n"/>
+      <c r="N83">
+        <f>IF($B83="","",$C83&amp;"|"&amp;COUNTIF($C$6:$C83,$C83))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="24" t="n"/>
@@ -5157,6 +5470,10 @@
         <v/>
       </c>
       <c r="L84" s="39" t="n"/>
+      <c r="N84">
+        <f>IF($B84="","",$C84&amp;"|"&amp;COUNTIF($C$6:$C84,$C84))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="B85" s="24" t="n"/>
@@ -5173,6 +5490,10 @@
         <v/>
       </c>
       <c r="L85" s="39" t="n"/>
+      <c r="N85">
+        <f>IF($B85="","",$C85&amp;"|"&amp;COUNTIF($C$6:$C85,$C85))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="24" t="n"/>
@@ -5189,6 +5510,10 @@
         <v/>
       </c>
       <c r="L86" s="39" t="n"/>
+      <c r="N86">
+        <f>IF($B86="","",$C86&amp;"|"&amp;COUNTIF($C$6:$C86,$C86))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="24" t="n"/>
@@ -5205,6 +5530,10 @@
         <v/>
       </c>
       <c r="L87" s="39" t="n"/>
+      <c r="N87">
+        <f>IF($B87="","",$C87&amp;"|"&amp;COUNTIF($C$6:$C87,$C87))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="24" t="n"/>
@@ -5221,6 +5550,10 @@
         <v/>
       </c>
       <c r="L88" s="39" t="n"/>
+      <c r="N88">
+        <f>IF($B88="","",$C88&amp;"|"&amp;COUNTIF($C$6:$C88,$C88))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="24" t="n"/>
@@ -5237,6 +5570,10 @@
         <v/>
       </c>
       <c r="L89" s="39" t="n"/>
+      <c r="N89">
+        <f>IF($B89="","",$C89&amp;"|"&amp;COUNTIF($C$6:$C89,$C89))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="B90" s="24" t="n"/>
@@ -5253,6 +5590,10 @@
         <v/>
       </c>
       <c r="L90" s="39" t="n"/>
+      <c r="N90">
+        <f>IF($B90="","",$C90&amp;"|"&amp;COUNTIF($C$6:$C90,$C90))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="B91" s="24" t="n"/>
@@ -5269,6 +5610,10 @@
         <v/>
       </c>
       <c r="L91" s="39" t="n"/>
+      <c r="N91">
+        <f>IF($B91="","",$C91&amp;"|"&amp;COUNTIF($C$6:$C91,$C91))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="24" t="n"/>
@@ -5285,6 +5630,10 @@
         <v/>
       </c>
       <c r="L92" s="39" t="n"/>
+      <c r="N92">
+        <f>IF($B92="","",$C92&amp;"|"&amp;COUNTIF($C$6:$C92,$C92))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="B93" s="24" t="n"/>
@@ -5301,6 +5650,10 @@
         <v/>
       </c>
       <c r="L93" s="39" t="n"/>
+      <c r="N93">
+        <f>IF($B93="","",$C93&amp;"|"&amp;COUNTIF($C$6:$C93,$C93))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="B94" s="24" t="n"/>
@@ -5317,6 +5670,10 @@
         <v/>
       </c>
       <c r="L94" s="39" t="n"/>
+      <c r="N94">
+        <f>IF($B94="","",$C94&amp;"|"&amp;COUNTIF($C$6:$C94,$C94))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="24" t="n"/>
@@ -5333,6 +5690,10 @@
         <v/>
       </c>
       <c r="L95" s="39" t="n"/>
+      <c r="N95">
+        <f>IF($B95="","",$C95&amp;"|"&amp;COUNTIF($C$6:$C95,$C95))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="B96" s="24" t="n"/>
@@ -5349,6 +5710,10 @@
         <v/>
       </c>
       <c r="L96" s="39" t="n"/>
+      <c r="N96">
+        <f>IF($B96="","",$C96&amp;"|"&amp;COUNTIF($C$6:$C96,$C96))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="B97" s="24" t="n"/>
@@ -5365,6 +5730,10 @@
         <v/>
       </c>
       <c r="L97" s="39" t="n"/>
+      <c r="N97">
+        <f>IF($B97="","",$C97&amp;"|"&amp;COUNTIF($C$6:$C97,$C97))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="B98" s="24" t="n"/>
@@ -5381,6 +5750,10 @@
         <v/>
       </c>
       <c r="L98" s="39" t="n"/>
+      <c r="N98">
+        <f>IF($B98="","",$C98&amp;"|"&amp;COUNTIF($C$6:$C98,$C98))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="B99" s="24" t="n"/>
@@ -5397,6 +5770,10 @@
         <v/>
       </c>
       <c r="L99" s="39" t="n"/>
+      <c r="N99">
+        <f>IF($B99="","",$C99&amp;"|"&amp;COUNTIF($C$6:$C99,$C99))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="B100" s="24" t="n"/>
@@ -5413,6 +5790,10 @@
         <v/>
       </c>
       <c r="L100" s="39" t="n"/>
+      <c r="N100">
+        <f>IF($B100="","",$C100&amp;"|"&amp;COUNTIF($C$6:$C100,$C100))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="24" t="n"/>
@@ -5429,6 +5810,10 @@
         <v/>
       </c>
       <c r="L101" s="39" t="n"/>
+      <c r="N101">
+        <f>IF($B101="","",$C101&amp;"|"&amp;COUNTIF($C$6:$C101,$C101))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="24" t="n"/>
@@ -5445,6 +5830,10 @@
         <v/>
       </c>
       <c r="L102" s="39" t="n"/>
+      <c r="N102">
+        <f>IF($B102="","",$C102&amp;"|"&amp;COUNTIF($C$6:$C102,$C102))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="24" t="n"/>
@@ -5461,6 +5850,10 @@
         <v/>
       </c>
       <c r="L103" s="39" t="n"/>
+      <c r="N103">
+        <f>IF($B103="","",$C103&amp;"|"&amp;COUNTIF($C$6:$C103,$C103))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="24" t="n"/>
@@ -5477,6 +5870,10 @@
         <v/>
       </c>
       <c r="L104" s="39" t="n"/>
+      <c r="N104">
+        <f>IF($B104="","",$C104&amp;"|"&amp;COUNTIF($C$6:$C104,$C104))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="24" t="n"/>
@@ -5493,6 +5890,10 @@
         <v/>
       </c>
       <c r="L105" s="39" t="n"/>
+      <c r="N105">
+        <f>IF($B105="","",$C105&amp;"|"&amp;COUNTIF($C$6:$C105,$C105))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B5:L105"/>
@@ -5763,7 +6164,7 @@
         <v/>
       </c>
       <c r="N11">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N11)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N11),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -5809,7 +6210,7 @@
         <v/>
       </c>
       <c r="N12">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N12)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N12),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -5855,7 +6256,7 @@
         <v/>
       </c>
       <c r="N13">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N13)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N13),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -5901,7 +6302,7 @@
         <v/>
       </c>
       <c r="N14">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N14)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N14),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -5947,7 +6348,7 @@
         <v/>
       </c>
       <c r="N15">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N15)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N15),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -5993,7 +6394,7 @@
         <v/>
       </c>
       <c r="N16">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N16)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N16),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6039,7 +6440,7 @@
         <v/>
       </c>
       <c r="N17">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N17)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N17),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6085,7 +6486,7 @@
         <v/>
       </c>
       <c r="N18">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N18)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N18),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6131,7 +6532,7 @@
         <v/>
       </c>
       <c r="N19">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N19)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N19),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6177,7 +6578,7 @@
         <v/>
       </c>
       <c r="N20">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N20)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N20),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6223,7 +6624,7 @@
         <v/>
       </c>
       <c r="N21">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N21)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N21),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6269,7 +6670,7 @@
         <v/>
       </c>
       <c r="N22">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N22)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N22),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6315,7 +6716,7 @@
         <v/>
       </c>
       <c r="N23">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N23)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N23),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6361,7 +6762,7 @@
         <v/>
       </c>
       <c r="N24">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N24)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N24),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6407,7 +6808,7 @@
         <v/>
       </c>
       <c r="N25">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N25)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N25),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6453,7 +6854,7 @@
         <v/>
       </c>
       <c r="N26">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N26)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N26),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6499,7 +6900,7 @@
         <v/>
       </c>
       <c r="N27">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N27)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N27),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6545,7 +6946,7 @@
         <v/>
       </c>
       <c r="N28">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N28)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N28),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6591,7 +6992,7 @@
         <v/>
       </c>
       <c r="N29">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N29)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N29),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6637,7 +7038,7 @@
         <v/>
       </c>
       <c r="N30">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N30)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N30),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6683,7 +7084,7 @@
         <v/>
       </c>
       <c r="N31">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N31)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N31),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6729,7 +7130,7 @@
         <v/>
       </c>
       <c r="N32">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N32)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N32),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6775,7 +7176,7 @@
         <v/>
       </c>
       <c r="N33">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N33)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N33),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6821,7 +7222,7 @@
         <v/>
       </c>
       <c r="N34">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N34)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N34),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6867,7 +7268,7 @@
         <v/>
       </c>
       <c r="N35">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N35)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N35),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6913,7 +7314,7 @@
         <v/>
       </c>
       <c r="N36">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N36)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N36),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -6959,7 +7360,7 @@
         <v/>
       </c>
       <c r="N37">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N37)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N37),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7005,7 +7406,7 @@
         <v/>
       </c>
       <c r="N38">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N38)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N38),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7051,7 +7452,7 @@
         <v/>
       </c>
       <c r="N39">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N39)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N39),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7097,7 +7498,7 @@
         <v/>
       </c>
       <c r="N40">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N40)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N40),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7143,7 +7544,7 @@
         <v/>
       </c>
       <c r="N41">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N41)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N41),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7189,7 +7590,7 @@
         <v/>
       </c>
       <c r="N42">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N42)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N42),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7235,7 +7636,7 @@
         <v/>
       </c>
       <c r="N43">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N43)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N43),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7281,7 +7682,7 @@
         <v/>
       </c>
       <c r="N44">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N44)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N44),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7327,7 +7728,7 @@
         <v/>
       </c>
       <c r="N45">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N45)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N45),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7373,7 +7774,7 @@
         <v/>
       </c>
       <c r="N46">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N46)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N46),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7419,7 +7820,7 @@
         <v/>
       </c>
       <c r="N47">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N47)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N47),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7465,7 +7866,7 @@
         <v/>
       </c>
       <c r="N48">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N48)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N48),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7511,7 +7912,7 @@
         <v/>
       </c>
       <c r="N49">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N49)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N49),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7557,7 +7958,7 @@
         <v/>
       </c>
       <c r="N50">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N50)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N50),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7603,7 +8004,7 @@
         <v/>
       </c>
       <c r="N51">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N51)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N51),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7649,7 +8050,7 @@
         <v/>
       </c>
       <c r="N52">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N52)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N52),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7695,7 +8096,7 @@
         <v/>
       </c>
       <c r="N53">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N53)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N53),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7741,7 +8142,7 @@
         <v/>
       </c>
       <c r="N54">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N54)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N54),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7787,7 +8188,7 @@
         <v/>
       </c>
       <c r="N55">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N55)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N55),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7833,7 +8234,7 @@
         <v/>
       </c>
       <c r="N56">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N56)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N56),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7879,7 +8280,7 @@
         <v/>
       </c>
       <c r="N57">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N57)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N57),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7925,7 +8326,7 @@
         <v/>
       </c>
       <c r="N58">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N58)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N58),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -7971,7 +8372,7 @@
         <v/>
       </c>
       <c r="N59">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N59)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N59),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8017,7 +8418,7 @@
         <v/>
       </c>
       <c r="N60">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N60)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N60),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8063,7 +8464,7 @@
         <v/>
       </c>
       <c r="N61">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N61)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N61),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8109,7 +8510,7 @@
         <v/>
       </c>
       <c r="N62">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N62)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N62),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8155,7 +8556,7 @@
         <v/>
       </c>
       <c r="N63">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N63)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N63),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8201,7 +8602,7 @@
         <v/>
       </c>
       <c r="N64">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N64)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N64),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8247,7 +8648,7 @@
         <v/>
       </c>
       <c r="N65">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N65)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N65),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8293,7 +8694,7 @@
         <v/>
       </c>
       <c r="N66">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N66)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N66),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8339,7 +8740,7 @@
         <v/>
       </c>
       <c r="N67">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N67)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N67),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8385,7 +8786,7 @@
         <v/>
       </c>
       <c r="N68">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N68)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N68),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8431,7 +8832,7 @@
         <v/>
       </c>
       <c r="N69">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N69)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N69),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
@@ -8477,7 +8878,7 @@
         <v/>
       </c>
       <c r="N70">
-        <f>IF($C$5="","",IFERROR(AGGREGATE(15,6,(ROW(작업!$C$6:$C$105)-5)/((작업!$C$6:$C$105=$C$5)*(작업!$B$6:$B$105&lt;&gt;"")),ROWS($N$11:$N70)),""))</f>
+        <f>IF($C$5="","",IFERROR(MATCH($C$5&amp;"|"&amp;ROWS($N$11:$N70),작업!$N$6:$N$105,0),""))</f>
         <v/>
       </c>
     </row>
